--- a/files/source-db/asp table list.xlsx
+++ b/files/source-db/asp table list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ibm-my.sharepoint.com/personal/miftah_choiri_ibm_com/Documents/IBM💼/PROJECTS🎯/OPPORTUNITY/LENOVO-REPORT/lenovo-apps/23072026 - DB Table/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ibm-my.sharepoint.com/personal/miftah_choiri_ibm_com/Documents/IBM💼/LEARNING👨‍💻/github/repository/public/learning/lenovo-apps/backup-deploy-lenovo-development-test/files/source-db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_F25DC773A252ABDACC1048D4E15E582C5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94076B7F-31C1-4950-9418-EC7009C6F823}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_F25DC773A252ABDACC1048D4E15E582C5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E10398FF-4893-46BC-B100-D470944CF1B9}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="0" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="0" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="945">
   <si>
     <t>NO</t>
   </si>
@@ -2374,10 +2374,551 @@
     <t>https://maps.app.goo.gl/jVhkVZirPvu966Dx9</t>
   </si>
   <si>
-    <t>Jl. Jawa No. 37 RT. 10 Kel. Sukamerindu - Kota Bengkulu - 38119</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Jl. Kayoon No. 14 Embong Kaliasin - Genteng Surabaya Jawa Timur 60271</t>
+    <t>asp002</t>
+  </si>
+  <si>
+    <t>Adi Wahana</t>
+  </si>
+  <si>
+    <t>CV Adi Wahana</t>
+  </si>
+  <si>
+    <t>IBM ADI WAHANA</t>
+  </si>
+  <si>
+    <t>Adi Wahana Computer &amp; IT Store</t>
+  </si>
+  <si>
+    <t>Kediri</t>
+  </si>
+  <si>
+    <t>Ruko Hayam Wuruk Trade Centre, Jl. Hayam Wuruk Blok D-5, Balowerti, Kec. Kota, Kota Kediri, Jawa Timur 64121</t>
+  </si>
+  <si>
+    <t>-7.814291166516101, 112.01569066826985</t>
+  </si>
+  <si>
+    <t>Jl. Teuku Umar 62 -64 Kediri</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/354XAV8x3xZtmUWP9</t>
+  </si>
+  <si>
+    <t>081357000999, 0354-694040</t>
+  </si>
+  <si>
+    <t>Monday - Friday : 08.00 AM- 16.30 PM Saturday : 08.00 AM- 14.00 PM</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>asp003</t>
+  </si>
+  <si>
+    <t>Alvatech</t>
+  </si>
+  <si>
+    <t>CV ALVATECH</t>
+  </si>
+  <si>
+    <t>IBM Alvatech</t>
+  </si>
+  <si>
+    <t>Jl. Lanto Dg. Pasewang No.39, Maricaya Sel., Kec. Mamajang, Kota Makassar, Sulawesi Selatan 90142</t>
+  </si>
+  <si>
+    <t>-5.151642870412669, 119.42016779524337</t>
+  </si>
+  <si>
+    <t>Jl. Lanto Dg. Pasewang No.39, Maricaya, Kec. Makassar, Kota Makassar, Sulawesi Selatan 90142</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/EZULkg7P8puGEiZ3A</t>
+  </si>
+  <si>
+    <t>62 813-5544-6488/0411-3624319 /0411-851955</t>
+  </si>
+  <si>
+    <t>Monday - Saturday : 09:00 AM - 05:00 PM, SUNDAY : 11:00 AM - 07 PM</t>
+  </si>
+  <si>
+    <t>asp012</t>
+  </si>
+  <si>
+    <t>Crystal Computer</t>
+  </si>
+  <si>
+    <t>PT KRISTAL KOMPUTERINDO PERKASA</t>
+  </si>
+  <si>
+    <t>Kep. Riau</t>
+  </si>
+  <si>
+    <t>Komplek Galaxy, Jl. Imam Bonjol No.10, Lubuk Baja Kota, Kec. Lubuk Baja, Kota Batam, Kepulauan Riau 29444</t>
+  </si>
+  <si>
+    <t>1.1428541323547938, 104.01513399913391</t>
+  </si>
+  <si>
+    <t>Komplek Galaxy Jl. Imam Bonjol No. 07 – 10 Batam</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Di4Cg36zR1FisK9q7</t>
+  </si>
+  <si>
+    <t>0778  - 454294/081266223922</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jl. Jawa No. 37 RT. 10 Kel. Sukamerindu - Kota Bengkulu - 38119  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Jl. Jawa No. 37 RT. 10 Kel. Sukamerindu - Kota Bengkulu - 38119</t>
+    </r>
+  </si>
+  <si>
+    <t>asp021</t>
+  </si>
+  <si>
+    <t>DMC KUPANG</t>
+  </si>
+  <si>
+    <t>CV Duta Multi Komputer</t>
+  </si>
+  <si>
+    <t>IBM DMC</t>
+  </si>
+  <si>
+    <t>DMC COMPUTER</t>
+  </si>
+  <si>
+    <t>Kupang</t>
+  </si>
+  <si>
+    <t>RJR5+3RX, Fatululi, Kec. Oebobo, Kota Kupang, Nusa Tenggara Tim.</t>
+  </si>
+  <si>
+    <t>-10.159573199011742, 123.60998013542657</t>
+  </si>
+  <si>
+    <t>Ruko Lontar Permai Jln R. W monginsidi III blok A / 21 - 22 Kupang NTT</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wvSfMLg744tHBS3F9</t>
+  </si>
+  <si>
+    <t>0380-820274 / 828333</t>
+  </si>
+  <si>
+    <t>NTT</t>
+  </si>
+  <si>
+    <t>asp033</t>
+  </si>
+  <si>
+    <t>Infonet Ambasador</t>
+  </si>
+  <si>
+    <t>PT Infonet Mitra Sejati</t>
+  </si>
+  <si>
+    <t>Mall Ambasador, Jl. Prof. DR. Satrio No.26 Lt 3, RT.11/RW.4, Kuningan, Karet Kuningan, Kecamatan Setiabudi, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12940</t>
+  </si>
+  <si>
+    <t>-6.223753921787925, 106.8268489575128</t>
+  </si>
+  <si>
+    <t>Jl. Prof. DR. Satrio, RT.5/RW.2 Mall Ambasador Lt.2 No.38-39 Jakarta Selatan</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/gPuJf5ajkEaPVvoN7</t>
+  </si>
+  <si>
+    <t>021-5762542, 87778380120</t>
+  </si>
+  <si>
+    <t>asp035</t>
+  </si>
+  <si>
+    <t>Infonet Mitra Sejati Bogor</t>
+  </si>
+  <si>
+    <t>PT INFONET MITRA SEJATI Bogor</t>
+  </si>
+  <si>
+    <t>Infonet Bogor jambu 2</t>
+  </si>
+  <si>
+    <t>Plaza Jambu Dua Bogor, Lantai LG Blok A11 No. 1, RT.01/RW.06, Bantarjati, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16143</t>
+  </si>
+  <si>
+    <t>-6.5689586586824555, 106.80849110604794</t>
+  </si>
+  <si>
+    <t>Plaza Jambu Dua Lt. Semi Dasar. Blok A11. No. 1, 2, 7 &amp; 8, Jl. A. Yani No. 1-8 Rt 01 Rw 06 Bantarjati kec. Bogor Utara , Kota Bogor</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/r2QYv47WLVtx4Zk16</t>
+  </si>
+  <si>
+    <t>0251-8356898</t>
+  </si>
+  <si>
+    <t>-6.56835</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>90222</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 90115</t>
+    </r>
+  </si>
+  <si>
+    <t>asp049</t>
+  </si>
+  <si>
+    <t>ITSC Point Square</t>
+  </si>
+  <si>
+    <t>IBM ITSC POINT SQUARE</t>
+  </si>
+  <si>
+    <t>ASUS - LENOVO Service Center Poins Square by ITSC</t>
+  </si>
+  <si>
+    <t>SAMPING LIFT HOTEL, JL RA KARTINI 1 MALL POINTS SQUARE LANTAI 2 48, RT.9/RW.7, Lb. Bulus, Kec. Cilandak, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12440</t>
+  </si>
+  <si>
+    <t>-6.289219302201084, 106.77830285074481</t>
+  </si>
+  <si>
+    <t>JL RA KARTINI NO 1 MALL POINTS SQUARE LANTAI 2 NO 48 Jakarta selatan</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1DXPghZXKyqfUpDR6</t>
+  </si>
+  <si>
+    <t>0821-2121-4175</t>
+  </si>
+  <si>
+    <r>
+      <t>Jl. Kusuma Bangsa 116-188, Surabaya Hi Tech Mall, lt. 2 Blok A26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Jl. Kayoon No. 14 Embong Kaliasin - Genteng Surabaya Jawa Timur 60271</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>60272</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 60271</t>
+    </r>
+  </si>
+  <si>
+    <t>asp055</t>
+  </si>
+  <si>
+    <t>KJB Surabaya</t>
+  </si>
+  <si>
+    <t>KJB</t>
+  </si>
+  <si>
+    <t>PJM Surabaya</t>
+  </si>
+  <si>
+    <t>Asus Service Partner Surabaya</t>
+  </si>
+  <si>
+    <t>Jl. Barata Jaya No.59 Blk A1, Baratajaya, Kec. Gubeng, Surabaya, Jawa Timur 60284</t>
+  </si>
+  <si>
+    <t>-7.298552078104986, 112.76001311534482</t>
+  </si>
+  <si>
+    <t>Jl. Baratajaya 59 Blok A1</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZkP3yk5skRGdSS7M9</t>
+  </si>
+  <si>
+    <t>031 5019500</t>
+  </si>
+  <si>
+    <t>asp062</t>
+  </si>
+  <si>
+    <t>Megatama COMPUTINDO</t>
+  </si>
+  <si>
+    <t>CV Megatama Solusindo</t>
+  </si>
+  <si>
+    <t>CV MEGATAMA SOLUSINDO</t>
+  </si>
+  <si>
+    <t>Megatama Computindo</t>
+  </si>
+  <si>
+    <t>Jl. Arif Rahman Hakim No.10B, Karawang Kulon, Kec. Karawang Bar., Karawang, Jawa Barat 41311</t>
+  </si>
+  <si>
+    <t>-6.301719997588589, 107.29537548143446</t>
+  </si>
+  <si>
+    <t>JL. ARIEF RACHMAN HAKIM NO.10B, KARAWANG BARAT</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/CZh3RAFXPPG4VQLx5</t>
+  </si>
+  <si>
+    <t>+622678409202, '+6281818499886</t>
+  </si>
+  <si>
+    <t>asp068</t>
+  </si>
+  <si>
+    <t>PT Mitra Infosarana Bandung</t>
+  </si>
+  <si>
+    <t>ITC Kosambi, Jl. Baranang Siang C32, Kb. Pisang, Kec. Sumur Bandung, Kota Bandung, Jawa Barat 40112</t>
+  </si>
+  <si>
+    <t>-6.918147029410593, 107.62181987350677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITC Kosambi C32 - Jl. Baranangsiang, Bandung </t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RQ2t3DyxeeBhAQtC9</t>
+  </si>
+  <si>
+    <t>+62 22 4261978, 4261979</t>
+  </si>
+  <si>
+    <t>asp070</t>
+  </si>
+  <si>
+    <t>PT Mitra Infosarana Surabaya</t>
+  </si>
+  <si>
+    <t>Ruko Manyar Garden Regency, JL. Raya Nginden Semolo, No. 101/Kav. 15,, Surabaya, 60118, Ngenden Jangkungan, Sukolilo, Menur Pumpungan, Sukolilo, Surabaya, East Java 60118</t>
+  </si>
+  <si>
+    <t>-7.299656264523901, 112.7716374084229</t>
+  </si>
+  <si>
+    <t>Ruko Manyar Garden Regency - Jl. Nginden Semolo 101/Kav 15 Surabaya</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/obbrJLgX5vzTkPZWA</t>
+  </si>
+  <si>
+    <t>+62 31 5993619, 5994297, 5994298</t>
+  </si>
+  <si>
+    <t>asp071</t>
+  </si>
+  <si>
+    <t>PT Solusi Inti Pratama</t>
+  </si>
+  <si>
+    <t>PT. Solusi Inti Pratama - Lenovo Service Center &amp; Chubbsafes Dealer</t>
+  </si>
+  <si>
+    <t>Jl. Raya Puputan No.64 Renon, Dangin Puri Klod, Kec. Denpasar Tim., Kota Denpasar, Bali 80234</t>
+  </si>
+  <si>
+    <t>-8.672610844543204, 115.22389623072425</t>
+  </si>
+  <si>
+    <t>Jl. Raya Puputan No. 64 Renon Denpasar</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QAdmBDpzd9QmWLHs9</t>
+  </si>
+  <si>
+    <t>asp073</t>
+  </si>
+  <si>
+    <t>PT. Alya Prima Vera</t>
+  </si>
+  <si>
+    <t>PT Alya Prima Vera</t>
+  </si>
+  <si>
+    <t>Sara Komputer</t>
+  </si>
+  <si>
+    <t>Palu</t>
+  </si>
+  <si>
+    <t>Jl. S. Parman, Besusu Tengah, Kec. Palu Tim., Kota Palu, Sulawesi Tengah 94118</t>
+  </si>
+  <si>
+    <t>-0.8884054781298837, 119.87896491352167</t>
+  </si>
+  <si>
+    <t>Jl. S. Parman No. 61 Palu</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/p5EkjSE9jhW5XHij6</t>
+  </si>
+  <si>
+    <t>0811 458 6614</t>
+  </si>
+  <si>
+    <t>Monday - Friday : 09:00 AM - 04:00 PM</t>
+  </si>
+  <si>
+    <t>asp074</t>
+  </si>
+  <si>
+    <t>PT. Suka Guna Indonesia</t>
+  </si>
+  <si>
+    <t>PT SUKA GUNA INDONESIA</t>
+  </si>
+  <si>
+    <t>Surya Motor Banjarmasin</t>
+  </si>
+  <si>
+    <t>Jalan A. Yani KM 3 Blok H-I-J No 216, Karang Mekar, Kec. Banjarmasin Tim., Kota Banjarmasin, Kalimantan Selatan 70234</t>
+  </si>
+  <si>
+    <t>-3.3276261280678443, 114.60755855814294</t>
+  </si>
+  <si>
+    <t>JL.A YANI KM.3,5 NO.6 SAMPING DEALER HONDA SURYA MOTOR - Banjarmasin</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/PpyoeHHjU31ZzMwN9</t>
+  </si>
+  <si>
+    <t>0511-6789347 / 62 895-1877-3107</t>
+  </si>
+  <si>
+    <t>asp079</t>
+  </si>
+  <si>
+    <t>Tekno Komputer</t>
+  </si>
+  <si>
+    <t>Jl. Tuanku Tambusai No.63/52, Kp. Tengah, Sukajadi, Kota Pekanbaru, Riau 28121</t>
+  </si>
+  <si>
+    <t>0.5084504109309443, 101.44295331210765</t>
+  </si>
+  <si>
+    <t>JL. TUANKU TAMBUSAI NO. 63 PEKANBARU</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GeSoKRZJ2XkADVvK9</t>
+  </si>
+  <si>
+    <t>asp082</t>
+  </si>
+  <si>
+    <t>Venes Padang</t>
+  </si>
+  <si>
+    <t>CV Venes Jaya</t>
+  </si>
+  <si>
+    <t>IBM Venes Jaya</t>
+  </si>
+  <si>
+    <t>CV.VENES JAYA</t>
+  </si>
+  <si>
+    <t>Jl. Veteran No.21, Purus, Kec. Padang Bar., Kota Padang, Sumatera Barat 25116</t>
+  </si>
+  <si>
+    <t>-0.9405011744491638, 100.35418510448919</t>
+  </si>
+  <si>
+    <t>jl. Veteran no. 19 padang</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oLSSxiQQsN8Uh1997</t>
+  </si>
+  <si>
+    <t>'0751-30583</t>
+  </si>
+  <si>
+    <t>asp083</t>
+  </si>
+  <si>
+    <t>VTECH KOMPUTER</t>
+  </si>
+  <si>
+    <t>PT VICTORY TECHNOLOGY ABADI</t>
+  </si>
+  <si>
+    <t>IBM VTECH KOMPUTER</t>
+  </si>
+  <si>
+    <t>V-Tech Computer</t>
+  </si>
+  <si>
+    <t>Jl. Gajah Mada No.11-12, Jelutung, Kec. Jelutung, Kota Jambi, Jambi 36124</t>
+  </si>
+  <si>
+    <t>-1.6143637771761588, 103.61275594094477</t>
+  </si>
+  <si>
+    <t>Jl Gajah Mada No 11-12, Jambi</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/K4UVBZJCKX1W45a7A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0741-43789 ext 102, </t>
+  </si>
+  <si>
+    <t>asp000</t>
+  </si>
+  <si>
+    <t>abcd1234</t>
+  </si>
+  <si>
+    <t>IBM Admin</t>
   </si>
 </sst>
 </file>
@@ -2393,7 +2934,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.000000"/>
     <numFmt numFmtId="169" formatCode="#,##0.00000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2500,8 +3041,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF121212"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF121212"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2544,8 +3111,20 @@
         <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -2795,6 +3374,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2803,7 +3415,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3216,12 +3828,87 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3506,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3681,148 +4368,148 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>4</v>
+      <c r="A3" s="33">
+        <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>42</v>
+        <v>780</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="27">
-        <v>30008292</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="14">
-        <v>6002359170</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>45</v>
+        <v>30008952</v>
+      </c>
+      <c r="E3" s="156" t="s">
+        <v>781</v>
+      </c>
+      <c r="F3" s="157" t="s">
+        <v>782</v>
+      </c>
+      <c r="G3" s="158">
+        <v>6002389520</v>
+      </c>
+      <c r="H3" s="158" t="s">
+        <v>783</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>46</v>
+        <v>784</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>47</v>
+        <v>785</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>48</v>
+        <v>786</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>49</v>
+        <v>787</v>
       </c>
       <c r="M3" s="30" t="s">
-        <v>50</v>
+        <v>788</v>
       </c>
       <c r="N3" s="31" t="s">
-        <v>51</v>
+        <v>789</v>
       </c>
       <c r="O3" s="32">
-        <v>45118</v>
+        <v>64129</v>
       </c>
       <c r="P3" s="20" t="s">
-        <v>52</v>
+        <v>790</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>47</v>
+        <v>785</v>
       </c>
       <c r="R3" s="22" t="s">
         <v>35</v>
       </c>
       <c r="S3" s="21">
-        <v>-6.7161780000000002</v>
+        <v>-7.8130920000000001</v>
       </c>
       <c r="T3" s="21">
-        <v>108.55936</v>
+        <v>112.022924</v>
       </c>
       <c r="U3" s="24" t="s">
-        <v>53</v>
+        <v>791</v>
       </c>
       <c r="V3" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W3" s="25" t="s">
-        <v>40</v>
+        <v>792</v>
       </c>
       <c r="X3" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="33">
-        <v>5</v>
+      <c r="A4" s="8">
+        <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>55</v>
+        <v>793</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="11">
-        <v>30000918</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="14">
-        <v>6002321338</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>56</v>
+      <c r="D4" s="32">
+        <v>30009926</v>
+      </c>
+      <c r="E4" s="156" t="s">
+        <v>794</v>
+      </c>
+      <c r="F4" s="157" t="s">
+        <v>795</v>
+      </c>
+      <c r="G4" s="158">
+        <v>6002393954</v>
+      </c>
+      <c r="H4" s="158" t="s">
+        <v>796</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>56</v>
+        <v>794</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>59</v>
+        <v>797</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>60</v>
+        <v>798</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>61</v>
+        <v>799</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="O4" s="19">
-        <v>23122</v>
+        <v>90141</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>63</v>
+        <v>801</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="R4" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="S4" s="34">
-        <v>-7.2555129999999997</v>
-      </c>
-      <c r="T4" s="34">
-        <v>112.75060999999999</v>
+        <v>133</v>
+      </c>
+      <c r="S4" s="159">
+        <v>-5.1516748999999997</v>
+      </c>
+      <c r="T4" s="160">
+        <v>119420232</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>53</v>
+        <v>802</v>
       </c>
       <c r="V4" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W4" s="25" t="s">
-        <v>40</v>
+        <v>792</v>
       </c>
       <c r="X4" s="22" t="s">
         <v>54</v>
@@ -3830,67 +4517,67 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="32">
-        <v>30008157</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>66</v>
+      <c r="D5" s="27">
+        <v>30008292</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>43</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="G5" s="14">
-        <v>6059329522</v>
+        <v>6002359170</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="M5" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="N5" s="36" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="31" t="s">
+        <v>51</v>
       </c>
       <c r="O5" s="32">
-        <v>52113</v>
+        <v>45118</v>
       </c>
       <c r="P5" s="20" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="Q5" s="21" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="R5" s="22" t="s">
         <v>35</v>
       </c>
       <c r="S5" s="21">
-        <v>-6.2915300094807183E-2</v>
+        <v>-6.7161780000000002</v>
       </c>
       <c r="T5" s="21">
-        <v>109.12000879999999</v>
+        <v>108.55936</v>
       </c>
       <c r="U5" s="24" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="V5" s="25" t="s">
         <v>39</v>
@@ -3898,73 +4585,73 @@
       <c r="W5" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X5" s="26" t="s">
-        <v>41</v>
+      <c r="X5" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>7</v>
+      <c r="A6" s="33">
+        <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="37">
-        <v>39000429</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>79</v>
+      <c r="D6" s="11">
+        <v>30000918</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G6" s="14">
-        <v>6002359297</v>
+        <v>6002321338</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="I6" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="K6" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="L6" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="M6" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="N6" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="O6" s="37">
-        <v>17433</v>
-      </c>
-      <c r="P6" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q6" s="22" t="s">
-        <v>88</v>
+        <v>56</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" s="19">
+        <v>23122</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="R6" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S6" s="42">
-        <v>-6.3750010000000001</v>
-      </c>
-      <c r="T6" s="42">
-        <v>106.916228</v>
-      </c>
-      <c r="U6" s="43" t="s">
-        <v>38</v>
+        <v>64</v>
+      </c>
+      <c r="S6" s="34">
+        <v>-7.2555129999999997</v>
+      </c>
+      <c r="T6" s="34">
+        <v>112.75060999999999</v>
+      </c>
+      <c r="U6" s="24" t="s">
+        <v>53</v>
       </c>
       <c r="V6" s="25" t="s">
         <v>39</v>
@@ -3973,72 +4660,72 @@
         <v>40</v>
       </c>
       <c r="X6" s="22" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
-        <v>8</v>
+      <c r="A7" s="8">
+        <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="32">
-        <v>30000920</v>
+        <v>30008157</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="G7" s="14">
-        <v>6002321436</v>
+        <v>6059329522</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="M7" s="21" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="N7" s="36" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="O7" s="32">
-        <v>10610</v>
+        <v>52113</v>
       </c>
       <c r="P7" s="20" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="R7" s="22" t="s">
         <v>35</v>
       </c>
       <c r="S7" s="21">
-        <v>-6.1657489999999999</v>
+        <v>-6.2915300094807183E-2</v>
       </c>
       <c r="T7" s="21">
-        <v>106.83913800000001</v>
+        <v>109.12000879999999</v>
       </c>
       <c r="U7" s="24" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="V7" s="25" t="s">
         <v>39</v>
@@ -4046,73 +4733,73 @@
       <c r="W7" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X7" s="22" t="s">
-        <v>54</v>
+      <c r="X7" s="26" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="44">
-        <v>30011345</v>
+      <c r="D8" s="37">
+        <v>39000429</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="G8" s="14">
-        <v>6031794568</v>
+        <v>6002359297</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>107</v>
+        <v>80</v>
+      </c>
+      <c r="I8" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" s="40" t="s">
+        <v>84</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="O8" s="37">
-        <v>75117</v>
-      </c>
-      <c r="P8" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q8" s="45" t="s">
-        <v>105</v>
+        <v>17433</v>
+      </c>
+      <c r="P8" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="22" t="s">
+        <v>88</v>
       </c>
       <c r="R8" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="S8" s="45">
-        <v>-0.48691800000000002</v>
-      </c>
-      <c r="T8" s="45">
-        <v>117.15469899999999</v>
-      </c>
-      <c r="U8" s="24" t="s">
-        <v>77</v>
+        <v>35</v>
+      </c>
+      <c r="S8" s="42">
+        <v>-6.3750010000000001</v>
+      </c>
+      <c r="T8" s="42">
+        <v>106.916228</v>
+      </c>
+      <c r="U8" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="V8" s="25" t="s">
         <v>39</v>
@@ -4121,72 +4808,72 @@
         <v>40</v>
       </c>
       <c r="X8" s="22" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>10</v>
+      <c r="A9" s="33">
+        <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="46">
-        <v>30011542</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>113</v>
+      <c r="D9" s="32">
+        <v>30000920</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>91</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="G9" s="14">
-        <v>6033554611</v>
+        <v>6002321436</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="M9" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="N9" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="O9" s="46">
-        <v>11610</v>
-      </c>
-      <c r="P9" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q9" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="O9" s="32">
+        <v>10610</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q9" s="21" t="s">
         <v>34</v>
       </c>
       <c r="R9" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="S9" s="20">
-        <v>106.7530263</v>
-      </c>
-      <c r="T9" s="49">
-        <v>-6.1859985999999996</v>
-      </c>
-      <c r="U9" s="43" t="s">
-        <v>38</v>
+      <c r="S9" s="21">
+        <v>-6.1657489999999999</v>
+      </c>
+      <c r="T9" s="21">
+        <v>106.83913800000001</v>
+      </c>
+      <c r="U9" s="24" t="s">
+        <v>53</v>
       </c>
       <c r="V9" s="25" t="s">
         <v>39</v>
@@ -4195,72 +4882,72 @@
         <v>40</v>
       </c>
       <c r="X9" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="33">
-        <v>11</v>
+      <c r="A10" s="8">
+        <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="11">
-        <v>30000921</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>123</v>
+      <c r="D10" s="44">
+        <v>30011345</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>101</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="G10" s="14">
-        <v>6002321489</v>
+        <v>6031794568</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="N10" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="O10" s="19">
-        <v>90151</v>
+        <v>107</v>
+      </c>
+      <c r="M10" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="N10" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="O10" s="37">
+        <v>75117</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q10" s="17" t="s">
-        <v>127</v>
+        <v>110</v>
+      </c>
+      <c r="Q10" s="45" t="s">
+        <v>105</v>
       </c>
       <c r="R10" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="S10" s="34">
-        <v>-5.1316050000000004</v>
-      </c>
-      <c r="T10" s="34">
-        <v>119.425141</v>
+        <v>111</v>
+      </c>
+      <c r="S10" s="45">
+        <v>-0.48691800000000002</v>
+      </c>
+      <c r="T10" s="45">
+        <v>117.15469899999999</v>
       </c>
       <c r="U10" s="24" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="V10" s="25" t="s">
         <v>39</v>
@@ -4274,67 +4961,67 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="50">
-        <v>30009407</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>135</v>
+      <c r="D11" s="46">
+        <v>30011542</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>113</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="G11" s="14">
-        <v>6002390291</v>
+        <v>6033554611</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="M11" s="30" t="s">
-        <v>141</v>
+        <v>118</v>
+      </c>
+      <c r="M11" s="48" t="s">
+        <v>119</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="O11" s="32">
-        <v>25134</v>
-      </c>
-      <c r="P11" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q11" s="21" t="s">
-        <v>138</v>
+        <v>120</v>
+      </c>
+      <c r="O11" s="46">
+        <v>11610</v>
+      </c>
+      <c r="P11" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="48" t="s">
+        <v>34</v>
       </c>
       <c r="R11" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="S11" s="21">
-        <v>-0.95682599999999995</v>
-      </c>
-      <c r="T11" s="21">
-        <v>100.363747</v>
-      </c>
-      <c r="U11" s="24" t="s">
-        <v>144</v>
+        <v>35</v>
+      </c>
+      <c r="S11" s="20">
+        <v>106.7530263</v>
+      </c>
+      <c r="T11" s="49">
+        <v>-6.1859985999999996</v>
+      </c>
+      <c r="U11" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="V11" s="25" t="s">
         <v>39</v>
@@ -4348,66 +5035,66 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="51">
-        <v>30000924</v>
+      <c r="D12" s="11">
+        <v>30000921</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="G12" s="14">
-        <v>6002321657</v>
+        <v>6002321489</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="I12" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="J12" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="K12" s="52" t="s">
-        <v>151</v>
-      </c>
-      <c r="L12" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="M12" s="156" t="s">
-        <v>780</v>
-      </c>
-      <c r="N12" s="54" t="s">
-        <v>153</v>
-      </c>
-      <c r="O12" s="55">
-        <v>38224</v>
-      </c>
-      <c r="P12" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q12" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="R12" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="S12" s="23">
-        <v>-3.8132229999999998</v>
-      </c>
-      <c r="T12" s="23">
-        <v>102.27587800000001</v>
-      </c>
-      <c r="U12" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="N12" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="O12" s="19">
+        <v>90151</v>
+      </c>
+      <c r="P12" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R12" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="S12" s="34">
+        <v>-5.1316050000000004</v>
+      </c>
+      <c r="T12" s="34">
+        <v>119.425141</v>
+      </c>
+      <c r="U12" s="24" t="s">
         <v>53</v>
       </c>
       <c r="V12" s="25" t="s">
@@ -4416,70 +5103,70 @@
       <c r="W12" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X12" s="60" t="s">
-        <v>41</v>
+      <c r="X12" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>155</v>
+        <v>803</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="11">
-        <v>30000925</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="G13" s="14">
-        <v>6002321684</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>156</v>
+      <c r="D13" s="32">
+        <v>30006510</v>
+      </c>
+      <c r="E13" s="161" t="s">
+        <v>804</v>
+      </c>
+      <c r="F13" s="157" t="s">
+        <v>805</v>
+      </c>
+      <c r="G13" s="158">
+        <v>6002350996</v>
+      </c>
+      <c r="H13" s="158" t="s">
+        <v>804</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>157</v>
+        <v>804</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>158</v>
+        <v>806</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>159</v>
+        <v>807</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="M13" s="17" t="s">
-        <v>161</v>
+        <v>808</v>
+      </c>
+      <c r="M13" s="70" t="s">
+        <v>809</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="O13" s="19">
-        <v>40112</v>
+        <v>810</v>
+      </c>
+      <c r="O13" s="32">
+        <v>29444</v>
       </c>
       <c r="P13" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>158</v>
+        <v>811</v>
+      </c>
+      <c r="Q13" s="21" t="s">
+        <v>223</v>
       </c>
       <c r="R13" s="22" t="s">
-        <v>35</v>
+        <v>223</v>
       </c>
       <c r="S13" s="34">
-        <v>-6.9185369999999997</v>
+        <v>1.146042</v>
       </c>
       <c r="T13" s="34">
-        <v>107.616563</v>
+        <v>104.011426</v>
       </c>
       <c r="U13" s="24" t="s">
         <v>53</v>
@@ -4488,75 +5175,75 @@
         <v>39</v>
       </c>
       <c r="W13" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="X13" s="26" t="s">
-        <v>41</v>
+        <v>792</v>
+      </c>
+      <c r="X13" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="37">
-        <v>30076759</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>165</v>
+      <c r="D14" s="50">
+        <v>30009407</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>135</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="G14" s="14">
-        <v>6048562975</v>
+        <v>6002390291</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I14" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="J14" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="K14" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="L14" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="M14" s="22" t="s">
-        <v>171</v>
+        <v>136</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="M14" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="N14" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="O14" s="61">
-        <v>15321</v>
-      </c>
-      <c r="P14" s="45">
-        <v>8979791919</v>
-      </c>
-      <c r="Q14" s="26" t="s">
-        <v>168</v>
+        <v>142</v>
+      </c>
+      <c r="O14" s="32">
+        <v>25134</v>
+      </c>
+      <c r="P14" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q14" s="21" t="s">
+        <v>138</v>
       </c>
       <c r="R14" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="S14" s="62">
-        <v>-6.2409860000000004</v>
-      </c>
-      <c r="T14" s="63">
-        <v>106.6299296</v>
-      </c>
-      <c r="U14" s="43" t="s">
-        <v>38</v>
+        <v>64</v>
+      </c>
+      <c r="S14" s="21">
+        <v>-0.95682599999999995</v>
+      </c>
+      <c r="T14" s="21">
+        <v>100.363747</v>
+      </c>
+      <c r="U14" s="24" t="s">
+        <v>144</v>
       </c>
       <c r="V14" s="25" t="s">
         <v>39</v>
@@ -4570,67 +5257,67 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="37">
-        <v>30010304</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="F15" s="64" t="s">
-        <v>175</v>
+      <c r="D15" s="51">
+        <v>30000924</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>147</v>
       </c>
       <c r="G15" s="14">
-        <v>6002394492</v>
+        <v>6002321657</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="N15" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="O15" s="32">
-        <v>26244</v>
-      </c>
-      <c r="P15" s="20">
-        <v>75293705</v>
-      </c>
-      <c r="Q15" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="R15" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="J15" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="K15" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="L15" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="M15" s="162" t="s">
+        <v>812</v>
+      </c>
+      <c r="N15" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="O15" s="55">
+        <v>38224</v>
+      </c>
+      <c r="P15" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q15" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="R15" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="S15" s="21">
-        <v>-0.23067299999999999</v>
-      </c>
-      <c r="T15" s="65">
-        <v>100.622574</v>
-      </c>
-      <c r="U15" s="24" t="s">
-        <v>183</v>
+      <c r="S15" s="23">
+        <v>-3.8132229999999998</v>
+      </c>
+      <c r="T15" s="23">
+        <v>102.27587800000001</v>
+      </c>
+      <c r="U15" s="59" t="s">
+        <v>53</v>
       </c>
       <c r="V15" s="25" t="s">
         <v>39</v>
@@ -4638,73 +5325,73 @@
       <c r="W15" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X15" s="22" t="s">
-        <v>54</v>
+      <c r="X15" s="60" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="37">
-        <v>30010322</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>185</v>
+      <c r="D16" s="11">
+        <v>30000925</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>156</v>
       </c>
       <c r="G16" s="14">
-        <v>6002394430</v>
+        <v>6002321684</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="M16" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="N16" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="O16" s="32">
-        <v>78122</v>
+        <v>160</v>
+      </c>
+      <c r="M16" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="N16" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="O16" s="19">
+        <v>40112</v>
       </c>
       <c r="P16" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q16" s="45" t="s">
-        <v>194</v>
+        <v>163</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="R16" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="S16" s="21">
-        <v>-3.1486E-2</v>
-      </c>
-      <c r="T16" s="21">
-        <v>109.342957</v>
+        <v>35</v>
+      </c>
+      <c r="S16" s="34">
+        <v>-6.9185369999999997</v>
+      </c>
+      <c r="T16" s="34">
+        <v>107.616563</v>
       </c>
       <c r="U16" s="24" t="s">
-        <v>195</v>
+        <v>53</v>
       </c>
       <c r="V16" s="25" t="s">
         <v>39</v>
@@ -4712,73 +5399,73 @@
       <c r="W16" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X16" s="22" t="s">
-        <v>54</v>
+      <c r="X16" s="26" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="11">
-        <v>30000927</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>197</v>
+      <c r="D17" s="37">
+        <v>30076759</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>165</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="G17" s="14">
-        <v>6002321297</v>
+        <v>6048562975</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="J17" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="M17" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="N17" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="O17" s="19">
-        <v>20111</v>
-      </c>
-      <c r="P17" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q17" s="17" t="s">
-        <v>200</v>
+        <v>166</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="K17" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="L17" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="M17" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="N17" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="O17" s="61">
+        <v>15321</v>
+      </c>
+      <c r="P17" s="45">
+        <v>8979791919</v>
+      </c>
+      <c r="Q17" s="26" t="s">
+        <v>168</v>
       </c>
       <c r="R17" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="S17" s="34">
-        <v>3.6013350000000002</v>
-      </c>
-      <c r="T17" s="34">
-        <v>98.673361</v>
-      </c>
-      <c r="U17" s="24" t="s">
-        <v>206</v>
+        <v>173</v>
+      </c>
+      <c r="S17" s="62">
+        <v>-6.2409860000000004</v>
+      </c>
+      <c r="T17" s="63">
+        <v>106.6299296</v>
+      </c>
+      <c r="U17" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="V17" s="25" t="s">
         <v>39</v>
@@ -4787,72 +5474,72 @@
         <v>40</v>
       </c>
       <c r="X17" s="22" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="33">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="32">
-        <v>30010627</v>
-      </c>
-      <c r="E18" s="66" t="s">
-        <v>208</v>
-      </c>
-      <c r="F18" s="66" t="s">
-        <v>208</v>
+      <c r="D18" s="37">
+        <v>30010304</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="64" t="s">
+        <v>175</v>
       </c>
       <c r="G18" s="14">
-        <v>6002394614</v>
+        <v>6002394492</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="M18" s="67" t="s">
-        <v>214</v>
-      </c>
-      <c r="N18" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="O18" s="68">
-        <v>99614</v>
+        <v>180</v>
+      </c>
+      <c r="M18" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="N18" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="O18" s="32">
+        <v>26244</v>
       </c>
       <c r="P18" s="20">
-        <v>82398010127</v>
-      </c>
-      <c r="Q18" s="26" t="s">
-        <v>216</v>
+        <v>75293705</v>
+      </c>
+      <c r="Q18" s="45" t="s">
+        <v>178</v>
       </c>
       <c r="R18" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="S18" s="69">
-        <v>-8.4813609999999997</v>
-      </c>
-      <c r="T18" s="67">
-        <v>140.38996800000001</v>
+        <v>64</v>
+      </c>
+      <c r="S18" s="21">
+        <v>-0.23067299999999999</v>
+      </c>
+      <c r="T18" s="65">
+        <v>100.622574</v>
       </c>
       <c r="U18" s="24" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="V18" s="25" t="s">
         <v>39</v>
@@ -4866,67 +5553,67 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="11">
-        <v>30000929</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>221</v>
+      <c r="D19" s="37">
+        <v>30010322</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>185</v>
       </c>
       <c r="G19" s="14">
-        <v>6002321482</v>
+        <v>6002394430</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="M19" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="N19" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="O19" s="19">
-        <v>29432</v>
+        <v>190</v>
+      </c>
+      <c r="M19" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="N19" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="O19" s="32">
+        <v>78122</v>
       </c>
       <c r="P19" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q19" s="17" t="s">
-        <v>223</v>
+        <v>193</v>
+      </c>
+      <c r="Q19" s="45" t="s">
+        <v>194</v>
       </c>
       <c r="R19" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="S19" s="34">
-        <v>1.128144</v>
-      </c>
-      <c r="T19" s="34">
-        <v>104.025588</v>
+        <v>111</v>
+      </c>
+      <c r="S19" s="21">
+        <v>-3.1486E-2</v>
+      </c>
+      <c r="T19" s="21">
+        <v>109.342957</v>
       </c>
       <c r="U19" s="24" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="V19" s="25" t="s">
         <v>39</v>
@@ -4934,73 +5621,73 @@
       <c r="W19" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X19" s="26" t="s">
-        <v>41</v>
+      <c r="X19" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A20" s="33">
-        <v>23</v>
+      <c r="A20" s="8">
+        <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="27">
-        <v>30008291</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>231</v>
+      <c r="D20" s="11">
+        <v>30000927</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="G20" s="14">
-        <v>6002359136</v>
+        <v>6002321297</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="M20" s="70" t="s">
-        <v>237</v>
+        <v>202</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>203</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="O20" s="37">
-        <v>33147</v>
+        <v>204</v>
+      </c>
+      <c r="O20" s="19">
+        <v>20111</v>
       </c>
       <c r="P20" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q20" s="21" t="s">
-        <v>240</v>
+        <v>205</v>
+      </c>
+      <c r="Q20" s="17" t="s">
+        <v>200</v>
       </c>
       <c r="R20" s="22" t="s">
-        <v>234</v>
+        <v>64</v>
       </c>
       <c r="S20" s="34">
-        <v>-2.135624</v>
+        <v>3.6013350000000002</v>
       </c>
       <c r="T20" s="34">
-        <v>106.126007</v>
+        <v>98.673361</v>
       </c>
       <c r="U20" s="24" t="s">
-        <v>53</v>
+        <v>206</v>
       </c>
       <c r="V20" s="25" t="s">
         <v>39</v>
@@ -5008,73 +5695,73 @@
       <c r="W20" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X20" s="26" t="s">
-        <v>41</v>
+      <c r="X20" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
-        <v>24</v>
+      <c r="A21" s="33">
+        <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="27">
-        <v>30006412</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>243</v>
+      <c r="D21" s="32">
+        <v>30010627</v>
+      </c>
+      <c r="E21" s="66" t="s">
+        <v>208</v>
+      </c>
+      <c r="F21" s="66" t="s">
+        <v>208</v>
       </c>
       <c r="G21" s="14">
-        <v>6002350290</v>
+        <v>6002394614</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="M21" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="N21" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="O21" s="32">
-        <v>36134</v>
-      </c>
-      <c r="P21" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q21" s="21" t="s">
-        <v>244</v>
+        <v>213</v>
+      </c>
+      <c r="M21" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="N21" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="O21" s="68">
+        <v>99614</v>
+      </c>
+      <c r="P21" s="20">
+        <v>82398010127</v>
+      </c>
+      <c r="Q21" s="26" t="s">
+        <v>216</v>
       </c>
       <c r="R21" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="S21" s="34">
-        <v>-1.5979289999999999</v>
-      </c>
-      <c r="T21" s="34">
-        <v>103.615532</v>
+        <v>217</v>
+      </c>
+      <c r="S21" s="69">
+        <v>-8.4813609999999997</v>
+      </c>
+      <c r="T21" s="67">
+        <v>140.38996800000001</v>
       </c>
       <c r="U21" s="24" t="s">
-        <v>53</v>
+        <v>218</v>
       </c>
       <c r="V21" s="25" t="s">
         <v>39</v>
@@ -5088,64 +5775,64 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>250</v>
+        <v>813</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="32">
-        <v>30006474</v>
-      </c>
-      <c r="E22" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="F22" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="G22" s="14">
-        <v>6002350920</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>251</v>
+        <v>30008778</v>
+      </c>
+      <c r="E22" s="161" t="s">
+        <v>814</v>
+      </c>
+      <c r="F22" s="157" t="s">
+        <v>815</v>
+      </c>
+      <c r="G22" s="158">
+        <v>6002389527</v>
+      </c>
+      <c r="H22" s="158" t="s">
+        <v>816</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>253</v>
+        <v>817</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>254</v>
+        <v>818</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>255</v>
+        <v>819</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="M22" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="N22" s="31" t="s">
-        <v>258</v>
+        <v>820</v>
+      </c>
+      <c r="M22" s="163" t="s">
+        <v>821</v>
+      </c>
+      <c r="N22" s="164" t="s">
+        <v>822</v>
       </c>
       <c r="O22" s="32">
-        <v>95113</v>
-      </c>
-      <c r="P22" s="20" t="s">
-        <v>259</v>
+        <v>85113</v>
+      </c>
+      <c r="P22" s="165" t="s">
+        <v>823</v>
       </c>
       <c r="Q22" s="21" t="s">
-        <v>254</v>
+        <v>818</v>
       </c>
       <c r="R22" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="S22" s="34">
-        <v>1.4828330000000001</v>
-      </c>
-      <c r="T22" s="34">
-        <v>124.833629</v>
+        <v>824</v>
+      </c>
+      <c r="S22" s="21">
+        <v>-10.183127000000001</v>
+      </c>
+      <c r="T22" s="166">
+        <v>123.583269</v>
       </c>
       <c r="U22" s="24" t="s">
         <v>53</v>
@@ -5154,75 +5841,75 @@
         <v>39</v>
       </c>
       <c r="W22" s="25" t="s">
-        <v>40</v>
+        <v>792</v>
       </c>
       <c r="X22" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A23" s="33">
-        <v>26</v>
+      <c r="A23" s="8">
+        <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="32">
-        <v>30000930</v>
-      </c>
-      <c r="E23" s="35" t="s">
-        <v>261</v>
+      <c r="D23" s="11">
+        <v>30000929</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="G23" s="14">
-        <v>6002321532</v>
+        <v>6002321482</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>262</v>
+        <v>222</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="M23" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="N23" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="O23" s="32">
-        <v>14240</v>
+        <v>225</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="N23" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="O23" s="19">
+        <v>29432</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q23" s="21" t="s">
-        <v>34</v>
+        <v>228</v>
+      </c>
+      <c r="Q23" s="17" t="s">
+        <v>223</v>
       </c>
       <c r="R23" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S23" s="23">
-        <v>-6.1588380000000003</v>
-      </c>
-      <c r="T23" s="23">
-        <v>106.894645</v>
+        <v>223</v>
+      </c>
+      <c r="S23" s="34">
+        <v>1.128144</v>
+      </c>
+      <c r="T23" s="34">
+        <v>104.025588</v>
       </c>
       <c r="U23" s="24" t="s">
-        <v>53</v>
+        <v>229</v>
       </c>
       <c r="V23" s="25" t="s">
         <v>39</v>
@@ -5235,68 +5922,68 @@
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
-        <v>27</v>
+      <c r="A24" s="33">
+        <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="37">
-        <v>30010321</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>270</v>
+      <c r="D24" s="27">
+        <v>30008291</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>232</v>
       </c>
       <c r="G24" s="14">
-        <v>6002394418</v>
+        <v>6002359136</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>272</v>
+        <v>220</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="M24" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="N24" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="O24" s="32">
-        <v>98312</v>
+        <v>236</v>
+      </c>
+      <c r="M24" s="70" t="s">
+        <v>237</v>
+      </c>
+      <c r="N24" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="O24" s="37">
+        <v>33147</v>
       </c>
       <c r="P24" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q24" s="45" t="s">
-        <v>279</v>
+        <v>239</v>
+      </c>
+      <c r="Q24" s="21" t="s">
+        <v>240</v>
       </c>
       <c r="R24" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="S24" s="21">
-        <v>-0.88277099999999997</v>
-      </c>
-      <c r="T24" s="21">
-        <v>134.04620399999999</v>
+        <v>234</v>
+      </c>
+      <c r="S24" s="34">
+        <v>-2.135624</v>
+      </c>
+      <c r="T24" s="34">
+        <v>106.126007</v>
       </c>
       <c r="U24" s="24" t="s">
-        <v>280</v>
+        <v>53</v>
       </c>
       <c r="V24" s="25" t="s">
         <v>39</v>
@@ -5304,70 +5991,70 @@
       <c r="W24" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X24" s="22" t="s">
-        <v>54</v>
+      <c r="X24" s="26" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="32">
-        <v>30008460</v>
+      <c r="D25" s="27">
+        <v>30006412</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="G25" s="14">
-        <v>6002359426</v>
+        <v>6002350290</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>127</v>
+        <v>244</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="M25" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="N25" s="31" t="s">
-        <v>289</v>
+        <v>246</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="N25" s="36" t="s">
+        <v>248</v>
       </c>
       <c r="O25" s="32">
-        <v>13620</v>
+        <v>36134</v>
       </c>
       <c r="P25" s="20" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="Q25" s="21" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="R25" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" s="71" t="s">
-        <v>291</v>
-      </c>
-      <c r="T25" s="71" t="s">
-        <v>292</v>
+        <v>64</v>
+      </c>
+      <c r="S25" s="34">
+        <v>-1.5979289999999999</v>
+      </c>
+      <c r="T25" s="34">
+        <v>103.615532</v>
       </c>
       <c r="U25" s="24" t="s">
         <v>53</v>
@@ -5383,68 +6070,68 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A26" s="33">
-        <v>29</v>
+      <c r="A26" s="8">
+        <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="32">
-        <v>30010576</v>
-      </c>
-      <c r="E26" s="66" t="s">
-        <v>294</v>
-      </c>
-      <c r="F26" s="72" t="s">
-        <v>294</v>
+        <v>30006474</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>252</v>
       </c>
       <c r="G26" s="14">
-        <v>6002394709</v>
+        <v>6002350920</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>298</v>
+        <v>255</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="M26" s="67" t="s">
-        <v>300</v>
-      </c>
-      <c r="N26" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="O26" s="68">
-        <v>97124</v>
+        <v>256</v>
+      </c>
+      <c r="M26" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="N26" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="O26" s="32">
+        <v>95113</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q26" s="26" t="s">
-        <v>303</v>
+        <v>259</v>
+      </c>
+      <c r="Q26" s="21" t="s">
+        <v>254</v>
       </c>
       <c r="R26" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="S26" s="69">
-        <v>128.183086</v>
-      </c>
-      <c r="T26" s="67">
-        <v>-3.697419</v>
+        <v>133</v>
+      </c>
+      <c r="S26" s="34">
+        <v>1.4828330000000001</v>
+      </c>
+      <c r="T26" s="34">
+        <v>124.833629</v>
       </c>
       <c r="U26" s="24" t="s">
-        <v>304</v>
+        <v>53</v>
       </c>
       <c r="V26" s="25" t="s">
         <v>39</v>
@@ -5457,68 +6144,68 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
-        <v>30</v>
+      <c r="A27" s="33">
+        <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="11">
-        <v>30000932</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>307</v>
+      <c r="D27" s="32">
+        <v>30000930</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>262</v>
       </c>
       <c r="G27" s="14">
-        <v>6002321677</v>
+        <v>6002321532</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>127</v>
+        <v>263</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="M27" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="N27" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="O27" s="19">
-        <v>90222</v>
+        <v>265</v>
+      </c>
+      <c r="M27" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="N27" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="O27" s="32">
+        <v>14240</v>
       </c>
       <c r="P27" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q27" s="17" t="s">
-        <v>127</v>
+        <v>268</v>
+      </c>
+      <c r="Q27" s="21" t="s">
+        <v>34</v>
       </c>
       <c r="R27" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="S27" s="34">
-        <v>-5.1386830000000003</v>
-      </c>
-      <c r="T27" s="34">
-        <v>119.412097</v>
+        <v>35</v>
+      </c>
+      <c r="S27" s="23">
+        <v>-6.1588380000000003</v>
+      </c>
+      <c r="T27" s="23">
+        <v>106.894645</v>
       </c>
       <c r="U27" s="24" t="s">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="V27" s="25" t="s">
         <v>39</v>
@@ -5532,67 +6219,67 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>315</v>
+        <v>269</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="73">
-        <v>30076472</v>
+      <c r="D28" s="37">
+        <v>30010321</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>317</v>
+        <v>270</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>270</v>
       </c>
       <c r="G28" s="14">
-        <v>6046836040</v>
+        <v>6002394418</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>319</v>
-      </c>
-      <c r="J28" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="K28" s="39" t="s">
-        <v>321</v>
-      </c>
-      <c r="L28" s="40" t="s">
-        <v>322</v>
+        <v>271</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>275</v>
       </c>
       <c r="M28" s="22" t="s">
-        <v>323</v>
+        <v>276</v>
       </c>
       <c r="N28" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="O28" s="37">
-        <v>81114</v>
-      </c>
-      <c r="P28" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q28" s="22" t="s">
-        <v>326</v>
+        <v>277</v>
+      </c>
+      <c r="O28" s="32">
+        <v>98312</v>
+      </c>
+      <c r="P28" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q28" s="45" t="s">
+        <v>279</v>
       </c>
       <c r="R28" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="S28" s="74">
-        <v>-8110656</v>
-      </c>
-      <c r="T28" s="75">
-        <v>115.08747</v>
-      </c>
-      <c r="U28" s="43" t="s">
-        <v>38</v>
+        <v>217</v>
+      </c>
+      <c r="S28" s="21">
+        <v>-0.88277099999999997</v>
+      </c>
+      <c r="T28" s="21">
+        <v>134.04620399999999</v>
+      </c>
+      <c r="U28" s="24" t="s">
+        <v>280</v>
       </c>
       <c r="V28" s="25" t="s">
         <v>39</v>
@@ -5601,72 +6288,72 @@
         <v>40</v>
       </c>
       <c r="X28" s="22" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="33">
-        <v>32</v>
+      <c r="A29" s="8">
+        <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>327</v>
+        <v>281</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D29" s="32">
-        <v>30004502</v>
+        <v>30008460</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="G29" s="14">
-        <v>6002341730</v>
+        <v>6002359426</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>331</v>
+        <v>127</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>332</v>
+        <v>286</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="M29" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="N29" s="18" t="s">
-        <v>335</v>
+        <v>287</v>
+      </c>
+      <c r="M29" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="N29" s="31" t="s">
+        <v>289</v>
       </c>
       <c r="O29" s="32">
-        <v>70117</v>
+        <v>13620</v>
       </c>
       <c r="P29" s="20" t="s">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="Q29" s="21" t="s">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="R29" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="S29" s="34">
-        <v>-3.3197459999999999</v>
-      </c>
-      <c r="T29" s="34">
-        <v>114.58515300000001</v>
+        <v>35</v>
+      </c>
+      <c r="S29" s="71" t="s">
+        <v>291</v>
+      </c>
+      <c r="T29" s="71" t="s">
+        <v>292</v>
       </c>
       <c r="U29" s="24" t="s">
-        <v>337</v>
+        <v>53</v>
       </c>
       <c r="V29" s="25" t="s">
         <v>39</v>
@@ -5674,73 +6361,73 @@
       <c r="W29" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X29" s="26" t="s">
-        <v>41</v>
+      <c r="X29" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
-        <v>34</v>
+      <c r="A30" s="33">
+        <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>338</v>
+        <v>293</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="76">
-        <v>30068998</v>
-      </c>
-      <c r="E30" s="77" t="s">
-        <v>339</v>
-      </c>
-      <c r="F30" s="64" t="s">
-        <v>340</v>
+      <c r="D30" s="32">
+        <v>30010576</v>
+      </c>
+      <c r="E30" s="66" t="s">
+        <v>294</v>
+      </c>
+      <c r="F30" s="72" t="s">
+        <v>294</v>
       </c>
       <c r="G30" s="14">
-        <v>6043498162</v>
+        <v>6002394709</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="I30" s="78" t="s">
-        <v>339</v>
-      </c>
-      <c r="J30" s="78" t="s">
-        <v>341</v>
-      </c>
-      <c r="K30" s="78" t="s">
-        <v>342</v>
-      </c>
-      <c r="L30" s="79" t="s">
-        <v>343</v>
-      </c>
-      <c r="M30" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="N30" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="O30" s="37">
-        <v>16424</v>
-      </c>
-      <c r="P30" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q30" s="22" t="s">
-        <v>341</v>
+        <v>295</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="M30" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="N30" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="O30" s="68">
+        <v>97124</v>
+      </c>
+      <c r="P30" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q30" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="R30" s="22" t="s">
-        <v>347</v>
-      </c>
-      <c r="S30" s="45">
-        <v>-6.3669634169112399</v>
-      </c>
-      <c r="T30" s="45">
-        <v>106.833852883635</v>
-      </c>
-      <c r="U30" s="43" t="s">
-        <v>348</v>
+        <v>297</v>
+      </c>
+      <c r="S30" s="69">
+        <v>128.183086</v>
+      </c>
+      <c r="T30" s="67">
+        <v>-3.697419</v>
+      </c>
+      <c r="U30" s="24" t="s">
+        <v>304</v>
       </c>
       <c r="V30" s="25" t="s">
         <v>39</v>
@@ -5749,72 +6436,72 @@
         <v>40</v>
       </c>
       <c r="X30" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="58">
-        <v>30011810</v>
-      </c>
-      <c r="E31" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="F31" s="80" t="s">
-        <v>351</v>
-      </c>
-      <c r="G31" s="81">
-        <v>6034339832</v>
-      </c>
-      <c r="H31" s="81" t="s">
-        <v>352</v>
+      <c r="D31" s="11">
+        <v>30000932</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="G31" s="14">
+        <v>6002321677</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>306</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>354</v>
+        <v>127</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>355</v>
+        <v>309</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="M31" s="48" t="s">
-        <v>357</v>
-      </c>
-      <c r="N31" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="O31" s="46">
-        <v>12760</v>
+        <v>310</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="N31" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="O31" s="19">
+        <v>90222</v>
       </c>
       <c r="P31" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q31" s="48" t="s">
-        <v>34</v>
+        <v>313</v>
+      </c>
+      <c r="Q31" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="R31" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S31" s="20">
-        <v>-6.2357471000000002</v>
-      </c>
-      <c r="T31" s="20">
-        <v>106.82480099999999</v>
-      </c>
-      <c r="U31" s="43" t="s">
-        <v>38</v>
+        <v>133</v>
+      </c>
+      <c r="S31" s="34">
+        <v>-5.1386830000000003</v>
+      </c>
+      <c r="T31" s="34">
+        <v>119.412097</v>
+      </c>
+      <c r="U31" s="24" t="s">
+        <v>314</v>
       </c>
       <c r="V31" s="25" t="s">
         <v>39</v>
@@ -5822,70 +6509,70 @@
       <c r="W31" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X31" s="22" t="s">
+      <c r="X31" s="26" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="82">
-        <v>30076540</v>
+      <c r="D32" s="73">
+        <v>30076472</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="F32" s="80" t="s">
-        <v>351</v>
+        <v>316</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>317</v>
       </c>
       <c r="G32" s="14">
-        <v>6047431287</v>
+        <v>6046836040</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="I32" s="39" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
       <c r="K32" s="39" t="s">
-        <v>365</v>
+        <v>321</v>
       </c>
       <c r="L32" s="40" t="s">
-        <v>366</v>
-      </c>
-      <c r="M32" s="83" t="s">
-        <v>367</v>
+        <v>322</v>
+      </c>
+      <c r="M32" s="22" t="s">
+        <v>323</v>
       </c>
       <c r="N32" s="31" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="O32" s="37">
-        <v>41361</v>
-      </c>
-      <c r="P32" s="84" t="s">
-        <v>369</v>
+        <v>81114</v>
+      </c>
+      <c r="P32" s="22" t="s">
+        <v>325</v>
       </c>
       <c r="Q32" s="22" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="R32" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="S32" s="85" t="s">
-        <v>370</v>
-      </c>
-      <c r="T32" s="86">
-        <v>107.266631312895</v>
+        <v>320</v>
+      </c>
+      <c r="S32" s="74">
+        <v>-8110656</v>
+      </c>
+      <c r="T32" s="75">
+        <v>115.08747</v>
       </c>
       <c r="U32" s="43" t="s">
         <v>38</v>
@@ -5900,293 +6587,365 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>371</v>
+        <v>327</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="82"/>
-      <c r="E33" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="F33" s="80" t="s">
-        <v>351</v>
-      </c>
-      <c r="G33" s="81">
-        <v>6041414615</v>
-      </c>
-      <c r="H33" s="81" t="s">
-        <v>373</v>
+      <c r="D33" s="32">
+        <v>30004502</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>328</v>
+      </c>
+      <c r="F33" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6002341730</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>328</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>374</v>
+        <v>330</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="M33" s="83" t="s">
-        <v>377</v>
-      </c>
-      <c r="N33" s="31" t="s">
-        <v>378</v>
-      </c>
-      <c r="O33" s="37"/>
-      <c r="P33" s="84"/>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="85"/>
-      <c r="T33" s="86"/>
-      <c r="U33" s="43"/>
+        <v>333</v>
+      </c>
+      <c r="M33" s="70" t="s">
+        <v>334</v>
+      </c>
+      <c r="N33" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="O33" s="32">
+        <v>70117</v>
+      </c>
+      <c r="P33" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q33" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="R33" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="S33" s="34">
+        <v>-3.3197459999999999</v>
+      </c>
+      <c r="T33" s="34">
+        <v>114.58515300000001</v>
+      </c>
+      <c r="U33" s="24" t="s">
+        <v>337</v>
+      </c>
       <c r="V33" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W33" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X33" s="22"/>
+      <c r="X33" s="26" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>379</v>
+        <v>825</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="82"/>
-      <c r="E34" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="F34" s="80" t="s">
-        <v>351</v>
-      </c>
-      <c r="G34" s="81">
-        <v>6041431901</v>
-      </c>
-      <c r="H34" s="81" t="s">
-        <v>381</v>
+      <c r="D34" s="167">
+        <v>30076512</v>
+      </c>
+      <c r="E34" s="168" t="s">
+        <v>826</v>
+      </c>
+      <c r="F34" s="169" t="s">
+        <v>340</v>
+      </c>
+      <c r="G34" s="158">
+        <v>6047084724</v>
+      </c>
+      <c r="H34" s="158" t="s">
+        <v>827</v>
       </c>
       <c r="I34" s="39" t="s">
-        <v>382</v>
+        <v>826</v>
       </c>
       <c r="J34" s="39" t="s">
-        <v>383</v>
+        <v>649</v>
       </c>
       <c r="K34" s="39" t="s">
-        <v>384</v>
+        <v>828</v>
       </c>
       <c r="L34" s="40" t="s">
-        <v>385</v>
-      </c>
-      <c r="M34" s="83" t="s">
-        <v>386</v>
+        <v>829</v>
+      </c>
+      <c r="M34" s="22" t="s">
+        <v>830</v>
       </c>
       <c r="N34" s="31" t="s">
-        <v>387</v>
-      </c>
-      <c r="O34" s="37"/>
-      <c r="P34" s="84"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="85"/>
-      <c r="T34" s="86"/>
-      <c r="U34" s="43"/>
+        <v>831</v>
+      </c>
+      <c r="O34" s="37">
+        <v>12940</v>
+      </c>
+      <c r="P34" s="26" t="s">
+        <v>832</v>
+      </c>
+      <c r="Q34" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="R34" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="S34" s="45">
+        <v>-6.2238304459225597</v>
+      </c>
+      <c r="T34" s="86">
+        <v>106.827405628609</v>
+      </c>
+      <c r="U34" s="43" t="s">
+        <v>38</v>
+      </c>
       <c r="V34" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W34" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="X34" s="22"/>
+        <v>792</v>
+      </c>
+      <c r="X34" s="22" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>388</v>
+        <v>338</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="82"/>
-      <c r="E35" s="38" t="s">
-        <v>389</v>
-      </c>
-      <c r="F35" s="80" t="s">
-        <v>351</v>
-      </c>
-      <c r="G35" s="81">
-        <v>6041431904</v>
-      </c>
-      <c r="H35" s="81" t="s">
-        <v>390</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>391</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="L35" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="M35" s="83" t="s">
-        <v>394</v>
+      <c r="D35" s="76">
+        <v>30068998</v>
+      </c>
+      <c r="E35" s="77" t="s">
+        <v>339</v>
+      </c>
+      <c r="F35" s="64" t="s">
+        <v>340</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6043498162</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="I35" s="78" t="s">
+        <v>339</v>
+      </c>
+      <c r="J35" s="78" t="s">
+        <v>341</v>
+      </c>
+      <c r="K35" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="L35" s="79" t="s">
+        <v>343</v>
+      </c>
+      <c r="M35" s="22" t="s">
+        <v>344</v>
       </c>
       <c r="N35" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="O35" s="37"/>
-      <c r="P35" s="84"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="85"/>
-      <c r="T35" s="86"/>
-      <c r="U35" s="43"/>
+        <v>345</v>
+      </c>
+      <c r="O35" s="37">
+        <v>16424</v>
+      </c>
+      <c r="P35" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q35" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="R35" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="S35" s="45">
+        <v>-6.3669634169112399</v>
+      </c>
+      <c r="T35" s="45">
+        <v>106.833852883635</v>
+      </c>
+      <c r="U35" s="43" t="s">
+        <v>348</v>
+      </c>
       <c r="V35" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W35" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X35" s="22"/>
+      <c r="X35" s="22" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>396</v>
+        <v>833</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="82"/>
-      <c r="E36" s="38" t="s">
-        <v>397</v>
-      </c>
-      <c r="F36" s="80" t="s">
-        <v>351</v>
-      </c>
-      <c r="G36" s="81">
-        <v>6041431896</v>
-      </c>
-      <c r="H36" s="81" t="s">
-        <v>398</v>
+      <c r="D36" s="37">
+        <v>30090465</v>
+      </c>
+      <c r="E36" s="168" t="s">
+        <v>834</v>
+      </c>
+      <c r="F36" s="169" t="s">
+        <v>340</v>
+      </c>
+      <c r="G36" s="158">
+        <v>6052266227</v>
+      </c>
+      <c r="H36" s="158" t="s">
+        <v>835</v>
       </c>
       <c r="I36" s="39" t="s">
-        <v>399</v>
+        <v>836</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="K36" s="39" t="s">
-        <v>400</v>
+        <v>837</v>
       </c>
       <c r="L36" s="40" t="s">
-        <v>401</v>
-      </c>
-      <c r="M36" s="83" t="s">
-        <v>402</v>
+        <v>838</v>
+      </c>
+      <c r="M36" s="170" t="s">
+        <v>839</v>
       </c>
       <c r="N36" s="31" t="s">
-        <v>403</v>
-      </c>
-      <c r="O36" s="37"/>
-      <c r="P36" s="84"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="85"/>
-      <c r="T36" s="86"/>
-      <c r="U36" s="43"/>
+        <v>840</v>
+      </c>
+      <c r="O36" s="37">
+        <v>16153</v>
+      </c>
+      <c r="P36" s="22" t="s">
+        <v>841</v>
+      </c>
+      <c r="Q36" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="R36" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="S36" s="85" t="s">
+        <v>842</v>
+      </c>
+      <c r="T36" s="171">
+        <v>106.80800000000001</v>
+      </c>
+      <c r="U36" s="43" t="s">
+        <v>38</v>
+      </c>
       <c r="V36" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W36" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="X36" s="22"/>
+        <v>792</v>
+      </c>
+      <c r="X36" s="22" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>404</v>
+        <v>349</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="27">
-        <v>30009875</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>405</v>
-      </c>
-      <c r="F37" s="29" t="s">
-        <v>406</v>
-      </c>
-      <c r="G37" s="14">
-        <v>6002394089</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>407</v>
+      <c r="D37" s="58">
+        <v>30011810</v>
+      </c>
+      <c r="E37" s="47" t="s">
+        <v>350</v>
+      </c>
+      <c r="F37" s="80" t="s">
+        <v>351</v>
+      </c>
+      <c r="G37" s="81">
+        <v>6034339832</v>
+      </c>
+      <c r="H37" s="81" t="s">
+        <v>352</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>408</v>
+        <v>353</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>409</v>
+        <v>354</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>410</v>
+        <v>355</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>411</v>
-      </c>
-      <c r="M37" s="17" t="s">
-        <v>412</v>
+        <v>356</v>
+      </c>
+      <c r="M37" s="48" t="s">
+        <v>357</v>
       </c>
       <c r="N37" s="31" t="s">
-        <v>413</v>
-      </c>
-      <c r="O37" s="19">
-        <v>83127</v>
+        <v>358</v>
+      </c>
+      <c r="O37" s="46">
+        <v>12760</v>
       </c>
       <c r="P37" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q37" s="17" t="s">
-        <v>415</v>
+        <v>359</v>
+      </c>
+      <c r="Q37" s="48" t="s">
+        <v>34</v>
       </c>
       <c r="R37" s="22" t="s">
-        <v>409</v>
-      </c>
-      <c r="S37" s="17">
-        <v>116.10108099999999</v>
-      </c>
-      <c r="T37" s="17">
-        <v>-8.6045069999999999</v>
-      </c>
-      <c r="U37" s="24" t="s">
-        <v>416</v>
+        <v>35</v>
+      </c>
+      <c r="S37" s="20">
+        <v>-6.2357471000000002</v>
+      </c>
+      <c r="T37" s="20">
+        <v>106.82480099999999</v>
+      </c>
+      <c r="U37" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="V37" s="25" t="s">
         <v>39</v>
@@ -6200,67 +6959,67 @@
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>417</v>
+        <v>360</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D38" s="11">
-        <v>30000956</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>419</v>
+      <c r="D38" s="82">
+        <v>30076540</v>
+      </c>
+      <c r="E38" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="F38" s="80" t="s">
+        <v>351</v>
       </c>
       <c r="G38" s="14">
-        <v>6002321713</v>
+        <v>6047431287</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>420</v>
+        <v>362</v>
       </c>
       <c r="I38" s="39" t="s">
-        <v>421</v>
+        <v>363</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>158</v>
+        <v>364</v>
       </c>
       <c r="K38" s="39" t="s">
-        <v>422</v>
+        <v>365</v>
       </c>
       <c r="L38" s="40" t="s">
-        <v>423</v>
-      </c>
-      <c r="M38" s="87" t="s">
-        <v>424</v>
+        <v>366</v>
+      </c>
+      <c r="M38" s="83" t="s">
+        <v>367</v>
       </c>
       <c r="N38" s="31" t="s">
-        <v>425</v>
-      </c>
-      <c r="O38" s="88">
-        <v>50113</v>
-      </c>
-      <c r="P38" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q38" s="17" t="s">
-        <v>158</v>
+        <v>368</v>
+      </c>
+      <c r="O38" s="37">
+        <v>41361</v>
+      </c>
+      <c r="P38" s="84" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q38" s="22" t="s">
+        <v>364</v>
       </c>
       <c r="R38" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S38" s="34">
-        <v>-6.9179170000000001</v>
-      </c>
-      <c r="T38" s="34">
-        <v>107.625513</v>
-      </c>
-      <c r="U38" s="24" t="s">
-        <v>427</v>
+        <v>173</v>
+      </c>
+      <c r="S38" s="85" t="s">
+        <v>370</v>
+      </c>
+      <c r="T38" s="86">
+        <v>107.266631312895</v>
+      </c>
+      <c r="U38" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="V38" s="25" t="s">
         <v>39</v>
@@ -6268,369 +7027,297 @@
       <c r="W38" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X38" s="26" t="s">
-        <v>41</v>
+      <c r="X38" s="22" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>428</v>
+        <v>371</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="32">
-        <v>30004372</v>
-      </c>
-      <c r="E39" s="35" t="s">
-        <v>429</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="G39" s="14">
-        <v>6002341647</v>
-      </c>
-      <c r="H39" s="14" t="s">
-        <v>430</v>
+      <c r="D39" s="82"/>
+      <c r="E39" s="38" t="s">
+        <v>372</v>
+      </c>
+      <c r="F39" s="80" t="s">
+        <v>351</v>
+      </c>
+      <c r="G39" s="81">
+        <v>6041414615</v>
+      </c>
+      <c r="H39" s="81" t="s">
+        <v>373</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>431</v>
+        <v>374</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>432</v>
+        <v>320</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>433</v>
+        <v>375</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>434</v>
-      </c>
-      <c r="M39" s="70" t="s">
-        <v>435</v>
+        <v>376</v>
+      </c>
+      <c r="M39" s="83" t="s">
+        <v>377</v>
       </c>
       <c r="N39" s="31" t="s">
-        <v>436</v>
-      </c>
-      <c r="O39" s="32">
-        <v>80113</v>
-      </c>
-      <c r="P39" s="45">
-        <v>82341626274</v>
-      </c>
-      <c r="Q39" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="R39" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="S39" s="89">
-        <v>-8.6802679999999999</v>
-      </c>
-      <c r="T39" s="90">
-        <v>115.20299</v>
-      </c>
-      <c r="U39" s="25" t="s">
-        <v>77</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="O39" s="37"/>
+      <c r="P39" s="84"/>
+      <c r="Q39" s="22"/>
+      <c r="R39" s="22"/>
+      <c r="S39" s="85"/>
+      <c r="T39" s="86"/>
+      <c r="U39" s="43"/>
       <c r="V39" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W39" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X39" s="26" t="s">
-        <v>41</v>
-      </c>
+      <c r="X39" s="22"/>
     </row>
-    <row r="40" spans="1:24" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>437</v>
+        <v>379</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="11">
-        <v>30000954</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="G40" s="14">
-        <v>6002321678</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>439</v>
+      <c r="D40" s="82"/>
+      <c r="E40" s="38" t="s">
+        <v>380</v>
+      </c>
+      <c r="F40" s="80" t="s">
+        <v>351</v>
+      </c>
+      <c r="G40" s="81">
+        <v>6041431901</v>
+      </c>
+      <c r="H40" s="81" t="s">
+        <v>381</v>
       </c>
       <c r="I40" s="39" t="s">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>28</v>
+        <v>383</v>
       </c>
       <c r="K40" s="39" t="s">
-        <v>441</v>
+        <v>384</v>
       </c>
       <c r="L40" s="40" t="s">
-        <v>442</v>
-      </c>
-      <c r="M40" s="91" t="s">
-        <v>443</v>
+        <v>385</v>
+      </c>
+      <c r="M40" s="83" t="s">
+        <v>386</v>
       </c>
       <c r="N40" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="O40" s="19">
-        <v>10160</v>
-      </c>
-      <c r="P40" s="92" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q40" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="R40" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S40" s="93">
-        <v>-6.1761559999999998</v>
-      </c>
-      <c r="T40" s="93">
-        <v>106.811842</v>
-      </c>
-      <c r="U40" s="24" t="s">
-        <v>446</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="O40" s="37"/>
+      <c r="P40" s="84"/>
+      <c r="Q40" s="22"/>
+      <c r="R40" s="22"/>
+      <c r="S40" s="85"/>
+      <c r="T40" s="86"/>
+      <c r="U40" s="43"/>
       <c r="V40" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W40" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X40" s="26" t="s">
-        <v>41</v>
-      </c>
+      <c r="X40" s="22"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>447</v>
+        <v>388</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="32">
-        <v>30010081</v>
-      </c>
-      <c r="E41" s="28" t="s">
-        <v>448</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="G41" s="14">
-        <v>6002394122</v>
-      </c>
-      <c r="H41" s="14" t="s">
-        <v>449</v>
+      <c r="D41" s="82"/>
+      <c r="E41" s="38" t="s">
+        <v>389</v>
+      </c>
+      <c r="F41" s="80" t="s">
+        <v>351</v>
+      </c>
+      <c r="G41" s="81">
+        <v>6041431904</v>
+      </c>
+      <c r="H41" s="81" t="s">
+        <v>390</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>451</v>
+        <v>158</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>452</v>
+        <v>392</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="M41" s="30" t="s">
-        <v>454</v>
+        <v>393</v>
+      </c>
+      <c r="M41" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="N41" s="31" t="s">
-        <v>455</v>
-      </c>
-      <c r="O41" s="32">
-        <v>59318</v>
-      </c>
-      <c r="P41" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q41" s="21" t="s">
-        <v>451</v>
-      </c>
-      <c r="R41" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S41" s="21">
-        <v>-6.8119540000000001</v>
-      </c>
-      <c r="T41" s="21">
-        <v>110.84168099999999</v>
-      </c>
-      <c r="U41" s="24" t="s">
-        <v>457</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="O41" s="37"/>
+      <c r="P41" s="84"/>
+      <c r="Q41" s="22"/>
+      <c r="R41" s="22"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="86"/>
+      <c r="U41" s="43"/>
       <c r="V41" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W41" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X41" s="22" t="s">
-        <v>54</v>
-      </c>
+      <c r="X41" s="22"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>458</v>
+        <v>396</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="11">
-        <v>30000961</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="G42" s="14">
-        <v>6002321440</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="L42" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="M42" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="N42" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="O42" s="19">
-        <v>90115</v>
-      </c>
-      <c r="P42" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="Q42" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="R42" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="S42" s="34">
-        <v>-5.1663949999999996</v>
-      </c>
-      <c r="T42" s="34">
-        <v>119.43403600000001</v>
-      </c>
-      <c r="U42" s="24" t="s">
-        <v>427</v>
-      </c>
+      <c r="D42" s="82"/>
+      <c r="E42" s="38" t="s">
+        <v>397</v>
+      </c>
+      <c r="F42" s="80" t="s">
+        <v>351</v>
+      </c>
+      <c r="G42" s="81">
+        <v>6041431896</v>
+      </c>
+      <c r="H42" s="81" t="s">
+        <v>398</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>399</v>
+      </c>
+      <c r="J42" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="K42" s="39" t="s">
+        <v>400</v>
+      </c>
+      <c r="L42" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="M42" s="83" t="s">
+        <v>402</v>
+      </c>
+      <c r="N42" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="O42" s="37"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="22"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="86"/>
+      <c r="U42" s="43"/>
       <c r="V42" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W42" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X42" s="26" t="s">
-        <v>41</v>
-      </c>
+      <c r="X42" s="22"/>
     </row>
-    <row r="43" spans="1:24" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>467</v>
+        <v>404</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D43" s="11">
-        <v>30000955</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>419</v>
+      <c r="D43" s="27">
+        <v>30009875</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>405</v>
+      </c>
+      <c r="F43" s="29" t="s">
+        <v>406</v>
       </c>
       <c r="G43" s="14">
-        <v>6002321698</v>
+        <v>6002394089</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>469</v>
+        <v>407</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>200</v>
+        <v>409</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>471</v>
-      </c>
-      <c r="L43" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="M43" s="94" t="s">
-        <v>473</v>
-      </c>
-      <c r="N43" s="18" t="s">
-        <v>474</v>
+        <v>410</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="M43" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="N43" s="31" t="s">
+        <v>413</v>
       </c>
       <c r="O43" s="19">
-        <v>20214</v>
-      </c>
-      <c r="P43" s="95" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q43" s="96" t="s">
-        <v>200</v>
-      </c>
-      <c r="R43" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="S43" s="98">
-        <v>3.5808</v>
-      </c>
-      <c r="T43" s="98">
-        <v>98.687205000000006</v>
-      </c>
-      <c r="U43" s="99" t="s">
-        <v>476</v>
+        <v>83127</v>
+      </c>
+      <c r="P43" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q43" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="R43" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="S43" s="17">
+        <v>116.10108099999999</v>
+      </c>
+      <c r="T43" s="17">
+        <v>-8.6045069999999999</v>
+      </c>
+      <c r="U43" s="24" t="s">
+        <v>416</v>
       </c>
       <c r="V43" s="25" t="s">
         <v>39</v>
@@ -6638,73 +7325,73 @@
       <c r="W43" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X43" s="95" t="s">
+      <c r="X43" s="22" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A44" s="33">
-        <v>50</v>
+      <c r="A44" s="8">
+        <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D44" s="11">
-        <v>30000957</v>
+        <v>30000956</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>478</v>
+        <v>418</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>419</v>
       </c>
       <c r="G44" s="14">
-        <v>6002321276</v>
+        <v>6002321713</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>480</v>
-      </c>
-      <c r="J44" s="15" t="s">
-        <v>481</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="L44" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="M44" s="22" t="s">
-        <v>484</v>
-      </c>
-      <c r="N44" s="100" t="s">
-        <v>485</v>
-      </c>
-      <c r="O44" s="19">
-        <v>50124</v>
+        <v>420</v>
+      </c>
+      <c r="I44" s="39" t="s">
+        <v>421</v>
+      </c>
+      <c r="J44" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="K44" s="39" t="s">
+        <v>422</v>
+      </c>
+      <c r="L44" s="40" t="s">
+        <v>423</v>
+      </c>
+      <c r="M44" s="87" t="s">
+        <v>424</v>
+      </c>
+      <c r="N44" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="O44" s="88">
+        <v>50113</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>486</v>
+        <v>426</v>
       </c>
       <c r="Q44" s="17" t="s">
-        <v>481</v>
+        <v>158</v>
       </c>
       <c r="R44" s="22" t="s">
         <v>35</v>
       </c>
       <c r="S44" s="34">
-        <v>-6.9924460000000002</v>
+        <v>-6.9179170000000001</v>
       </c>
       <c r="T44" s="34">
-        <v>110.432023</v>
+        <v>107.625513</v>
       </c>
       <c r="U44" s="24" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
       <c r="V44" s="25" t="s">
         <v>39</v>
@@ -6717,68 +7404,68 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
-        <v>51</v>
+      <c r="A45" s="33">
+        <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>488</v>
+        <v>428</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D45" s="11">
-        <v>30000959</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>489</v>
+      <c r="D45" s="32">
+        <v>30004372</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>429</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>419</v>
       </c>
       <c r="G45" s="14">
-        <v>6002321365</v>
+        <v>6002341647</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>491</v>
+        <v>431</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>492</v>
+        <v>433</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="M45" s="157" t="s">
-        <v>781</v>
-      </c>
-      <c r="N45" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="O45" s="19">
-        <v>60271</v>
-      </c>
-      <c r="P45" s="20" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q45" s="17" t="s">
-        <v>383</v>
+        <v>434</v>
+      </c>
+      <c r="M45" s="70" t="s">
+        <v>435</v>
+      </c>
+      <c r="N45" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="O45" s="32">
+        <v>80113</v>
+      </c>
+      <c r="P45" s="45">
+        <v>82341626274</v>
+      </c>
+      <c r="Q45" s="21" t="s">
+        <v>432</v>
       </c>
       <c r="R45" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S45" s="34">
-        <v>-7.2523790000000004</v>
-      </c>
-      <c r="T45" s="34">
-        <v>112.75036299999999</v>
-      </c>
-      <c r="U45" s="24" t="s">
-        <v>496</v>
+        <v>320</v>
+      </c>
+      <c r="S45" s="89">
+        <v>-8.6802679999999999</v>
+      </c>
+      <c r="T45" s="90">
+        <v>115.20299</v>
+      </c>
+      <c r="U45" s="25" t="s">
+        <v>77</v>
       </c>
       <c r="V45" s="25" t="s">
         <v>39</v>
@@ -6790,69 +7477,69 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D46" s="11">
-        <v>30000958</v>
+        <v>30000954</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>498</v>
+        <v>438</v>
       </c>
       <c r="F46" s="13" t="s">
         <v>419</v>
       </c>
       <c r="G46" s="14">
-        <v>6002321325</v>
+        <v>6002321678</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>499</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>500</v>
-      </c>
-      <c r="J46" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="L46" s="16" t="s">
-        <v>503</v>
-      </c>
-      <c r="M46" s="17" t="s">
-        <v>504</v>
-      </c>
-      <c r="N46" s="18" t="s">
-        <v>505</v>
+        <v>439</v>
+      </c>
+      <c r="I46" s="39" t="s">
+        <v>440</v>
+      </c>
+      <c r="J46" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="K46" s="39" t="s">
+        <v>441</v>
+      </c>
+      <c r="L46" s="40" t="s">
+        <v>442</v>
+      </c>
+      <c r="M46" s="91" t="s">
+        <v>443</v>
+      </c>
+      <c r="N46" s="31" t="s">
+        <v>444</v>
       </c>
       <c r="O46" s="19">
-        <v>55281</v>
-      </c>
-      <c r="P46" s="20" t="s">
-        <v>506</v>
+        <v>10160</v>
+      </c>
+      <c r="P46" s="92" t="s">
+        <v>445</v>
       </c>
       <c r="Q46" s="17" t="s">
-        <v>501</v>
+        <v>34</v>
       </c>
       <c r="R46" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="S46" s="34">
-        <v>-7.8010229999999998</v>
-      </c>
-      <c r="T46" s="34">
-        <v>110.373188</v>
+      <c r="S46" s="93">
+        <v>-6.1761559999999998</v>
+      </c>
+      <c r="T46" s="93">
+        <v>106.811842</v>
       </c>
       <c r="U46" s="24" t="s">
-        <v>496</v>
+        <v>446</v>
       </c>
       <c r="V46" s="25" t="s">
         <v>39</v>
@@ -6865,68 +7552,68 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A47" s="33">
-        <v>53</v>
+      <c r="A47" s="8">
+        <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>507</v>
+        <v>447</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D47" s="37">
-        <v>30011112</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>508</v>
-      </c>
-      <c r="F47" s="38" t="s">
-        <v>508</v>
+      <c r="D47" s="32">
+        <v>30010081</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>448</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="G47" s="14">
-        <v>6020996056</v>
+        <v>6002394122</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>509</v>
+        <v>449</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>138</v>
+        <v>451</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>511</v>
+        <v>452</v>
       </c>
       <c r="L47" s="16" t="s">
-        <v>512</v>
-      </c>
-      <c r="M47" s="22" t="s">
-        <v>513</v>
+        <v>453</v>
+      </c>
+      <c r="M47" s="30" t="s">
+        <v>454</v>
       </c>
       <c r="N47" s="31" t="s">
-        <v>514</v>
+        <v>455</v>
       </c>
       <c r="O47" s="32">
-        <v>25211</v>
+        <v>59318</v>
       </c>
       <c r="P47" s="20" t="s">
-        <v>515</v>
-      </c>
-      <c r="Q47" s="45" t="s">
-        <v>138</v>
+        <v>456</v>
+      </c>
+      <c r="Q47" s="21" t="s">
+        <v>451</v>
       </c>
       <c r="R47" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="S47" s="45">
-        <v>-0.95997399999999999</v>
-      </c>
-      <c r="T47" s="45">
-        <v>100.363501</v>
+        <v>35</v>
+      </c>
+      <c r="S47" s="21">
+        <v>-6.8119540000000001</v>
+      </c>
+      <c r="T47" s="21">
+        <v>110.84168099999999</v>
       </c>
       <c r="U47" s="24" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="V47" s="25" t="s">
         <v>39</v>
@@ -6935,72 +7622,72 @@
         <v>40</v>
       </c>
       <c r="X47" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
-        <v>54</v>
+      <c r="A48" s="33">
+        <v>47</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>516</v>
+        <v>458</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D48" s="32">
-        <v>30000963</v>
-      </c>
-      <c r="E48" s="35" t="s">
-        <v>517</v>
-      </c>
-      <c r="F48" s="29" t="s">
-        <v>518</v>
+      <c r="D48" s="11">
+        <v>30000961</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="G48" s="14">
-        <v>6002321533</v>
+        <v>6002321440</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>517</v>
+        <v>460</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>519</v>
+        <v>461</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>520</v>
+        <v>462</v>
       </c>
       <c r="L48" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="M48" s="70" t="s">
-        <v>522</v>
+        <v>463</v>
+      </c>
+      <c r="M48" s="17" t="s">
+        <v>464</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>523</v>
-      </c>
-      <c r="O48" s="32">
-        <v>11250</v>
-      </c>
-      <c r="P48" s="45" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q48" s="21" t="s">
-        <v>34</v>
+        <v>465</v>
+      </c>
+      <c r="O48" s="19" t="s">
+        <v>843</v>
+      </c>
+      <c r="P48" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q48" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="R48" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S48" s="23">
-        <v>-6.1466149999999997</v>
-      </c>
-      <c r="T48" s="23">
-        <v>106.80638399999999</v>
+        <v>133</v>
+      </c>
+      <c r="S48" s="34">
+        <v>-5.1663949999999996</v>
+      </c>
+      <c r="T48" s="34">
+        <v>119.43403600000001</v>
       </c>
       <c r="U48" s="24" t="s">
-        <v>53</v>
+        <v>427</v>
       </c>
       <c r="V48" s="25" t="s">
         <v>39</v>
@@ -7012,65 +7699,69 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A49" s="33">
-        <v>56</v>
+    <row r="49" spans="1:24" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>48</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>525</v>
+        <v>467</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D49" s="37">
-        <v>30010995</v>
-      </c>
-      <c r="E49" s="101" t="s">
-        <v>526</v>
-      </c>
-      <c r="F49" s="101" t="s">
-        <v>527</v>
-      </c>
-      <c r="G49" s="64"/>
-      <c r="H49" s="64"/>
+      <c r="D49" s="11">
+        <v>30000955</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="G49" s="14">
+        <v>6002321698</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>469</v>
+      </c>
       <c r="I49" s="15" t="s">
-        <v>528</v>
+        <v>470</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>529</v>
+        <v>200</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="L49" s="16" t="s">
-        <v>531</v>
-      </c>
-      <c r="M49" s="22" t="s">
-        <v>532</v>
-      </c>
-      <c r="N49" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="O49" s="32">
-        <v>79672</v>
-      </c>
-      <c r="P49" s="20">
-        <v>6256822888</v>
-      </c>
-      <c r="Q49" s="45" t="s">
-        <v>534</v>
-      </c>
-      <c r="R49" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="S49" s="102" t="s">
-        <v>535</v>
-      </c>
-      <c r="T49" s="102" t="s">
-        <v>536</v>
-      </c>
-      <c r="U49" s="24" t="s">
-        <v>537</v>
+        <v>471</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="M49" s="94" t="s">
+        <v>473</v>
+      </c>
+      <c r="N49" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="O49" s="19">
+        <v>20214</v>
+      </c>
+      <c r="P49" s="95" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q49" s="96" t="s">
+        <v>200</v>
+      </c>
+      <c r="R49" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="S49" s="98">
+        <v>3.5808</v>
+      </c>
+      <c r="T49" s="98">
+        <v>98.687205000000006</v>
+      </c>
+      <c r="U49" s="99" t="s">
+        <v>476</v>
       </c>
       <c r="V49" s="25" t="s">
         <v>39</v>
@@ -7078,147 +7769,147 @@
       <c r="W49" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X49" s="22" t="s">
-        <v>54</v>
+      <c r="X49" s="95" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>538</v>
+        <v>844</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D50" s="44">
-        <v>30010744</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>539</v>
-      </c>
-      <c r="F50" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="G50" s="14">
-        <v>6002398050</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>540</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>539</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>541</v>
-      </c>
-      <c r="K50" s="15" t="s">
-        <v>542</v>
-      </c>
-      <c r="L50" s="16" t="s">
-        <v>543</v>
-      </c>
-      <c r="M50" s="103" t="s">
-        <v>544</v>
-      </c>
-      <c r="N50" s="18" t="s">
-        <v>545</v>
-      </c>
-      <c r="O50" s="32">
-        <v>42162</v>
-      </c>
-      <c r="P50" s="20" t="s">
-        <v>546</v>
+      <c r="D50" s="37">
+        <v>30001032</v>
+      </c>
+      <c r="E50" s="168" t="s">
+        <v>845</v>
+      </c>
+      <c r="F50" s="172" t="s">
+        <v>419</v>
+      </c>
+      <c r="G50" s="158">
+        <v>6002359177</v>
+      </c>
+      <c r="H50" s="158" t="s">
+        <v>846</v>
+      </c>
+      <c r="I50" s="39" t="s">
+        <v>847</v>
+      </c>
+      <c r="J50" s="39" t="s">
+        <v>649</v>
+      </c>
+      <c r="K50" s="39" t="s">
+        <v>848</v>
+      </c>
+      <c r="L50" s="40" t="s">
+        <v>849</v>
+      </c>
+      <c r="M50" s="22" t="s">
+        <v>850</v>
+      </c>
+      <c r="N50" s="31" t="s">
+        <v>851</v>
+      </c>
+      <c r="O50" s="37">
+        <v>12440</v>
+      </c>
+      <c r="P50" s="84" t="s">
+        <v>852</v>
       </c>
       <c r="Q50" s="21" t="s">
-        <v>547</v>
+        <v>34</v>
       </c>
       <c r="R50" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="S50" s="21">
-        <v>-6.1104950000000002</v>
-      </c>
-      <c r="T50" s="21">
-        <v>106.117316</v>
-      </c>
-      <c r="U50" s="24" t="s">
-        <v>548</v>
+      <c r="S50" s="67">
+        <v>-6.2999400000000003</v>
+      </c>
+      <c r="T50" s="45">
+        <v>106.77800999999999</v>
+      </c>
+      <c r="U50" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="V50" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W50" s="25" t="s">
-        <v>40</v>
+        <v>792</v>
       </c>
       <c r="X50" s="22" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
-        <v>58</v>
+      <c r="A51" s="33">
+        <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>549</v>
+        <v>477</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D51" s="37">
-        <v>30090385</v>
-      </c>
-      <c r="E51" s="38" t="s">
-        <v>550</v>
-      </c>
-      <c r="F51" s="29" t="s">
-        <v>550</v>
+      <c r="D51" s="11">
+        <v>30000957</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="G51" s="14">
-        <v>6052078391</v>
+        <v>6002321276</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>551</v>
-      </c>
-      <c r="I51" s="39" t="s">
-        <v>552</v>
-      </c>
-      <c r="J51" s="39" t="s">
-        <v>553</v>
-      </c>
-      <c r="K51" s="39" t="s">
-        <v>554</v>
-      </c>
-      <c r="L51" s="40" t="s">
-        <v>555</v>
+        <v>479</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>483</v>
       </c>
       <c r="M51" s="22" t="s">
-        <v>556</v>
-      </c>
-      <c r="N51" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="O51" s="104">
-        <v>92713</v>
-      </c>
-      <c r="P51" s="22" t="s">
-        <v>558</v>
-      </c>
-      <c r="Q51" s="22" t="s">
-        <v>559</v>
+        <v>484</v>
+      </c>
+      <c r="N51" s="100" t="s">
+        <v>485</v>
+      </c>
+      <c r="O51" s="19">
+        <v>50124</v>
+      </c>
+      <c r="P51" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q51" s="17" t="s">
+        <v>481</v>
       </c>
       <c r="R51" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="S51" s="74">
-        <v>-8110656</v>
-      </c>
-      <c r="T51" s="62">
-        <v>115.08747</v>
-      </c>
-      <c r="U51" s="43" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="S51" s="34">
+        <v>-6.9924460000000002</v>
+      </c>
+      <c r="T51" s="34">
+        <v>110.432023</v>
+      </c>
+      <c r="U51" s="24" t="s">
+        <v>487</v>
       </c>
       <c r="V51" s="25" t="s">
         <v>39</v>
@@ -7226,73 +7917,73 @@
       <c r="W51" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X51" s="22" t="s">
-        <v>89</v>
+      <c r="X51" s="26" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A52" s="33">
-        <v>59</v>
+      <c r="A52" s="8">
+        <v>51</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>560</v>
+        <v>488</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D52" s="32">
-        <v>30010548</v>
-      </c>
-      <c r="E52" s="105" t="s">
-        <v>561</v>
-      </c>
-      <c r="F52" s="29" t="s">
-        <v>562</v>
+      <c r="D52" s="11">
+        <v>30000959</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="G52" s="14">
-        <v>6002394912</v>
+        <v>6002321365</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>563</v>
+        <v>490</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>561</v>
+        <v>491</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>564</v>
+        <v>383</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>565</v>
+        <v>492</v>
       </c>
       <c r="L52" s="16" t="s">
-        <v>566</v>
-      </c>
-      <c r="M52" s="30" t="s">
-        <v>567</v>
-      </c>
-      <c r="N52" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="O52" s="32">
-        <v>99111</v>
+        <v>493</v>
+      </c>
+      <c r="M52" s="173" t="s">
+        <v>853</v>
+      </c>
+      <c r="N52" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="O52" s="19" t="s">
+        <v>854</v>
       </c>
       <c r="P52" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="Q52" s="21" t="s">
-        <v>564</v>
+        <v>495</v>
+      </c>
+      <c r="Q52" s="17" t="s">
+        <v>383</v>
       </c>
       <c r="R52" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="S52" s="21">
-        <v>-2.5894029999999999</v>
-      </c>
-      <c r="T52" s="21">
-        <v>140.38442599999999</v>
+        <v>35</v>
+      </c>
+      <c r="S52" s="34">
+        <v>-7.2523790000000004</v>
+      </c>
+      <c r="T52" s="34">
+        <v>112.75036299999999</v>
       </c>
       <c r="U52" s="24" t="s">
-        <v>77</v>
+        <v>496</v>
       </c>
       <c r="V52" s="25" t="s">
         <v>39</v>
@@ -7300,73 +7991,73 @@
       <c r="W52" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X52" s="22" t="s">
-        <v>54</v>
+      <c r="X52" s="26" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>570</v>
+        <v>497</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D53" s="11">
-        <v>30000966</v>
+        <v>30000958</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="F53" s="29" t="s">
-        <v>572</v>
+        <v>498</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="G53" s="14">
-        <v>6002321630</v>
+        <v>6002321325</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>571</v>
+        <v>499</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>573</v>
+        <v>500</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>574</v>
+        <v>501</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>575</v>
+        <v>502</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>576</v>
+        <v>503</v>
       </c>
       <c r="M53" s="17" t="s">
-        <v>577</v>
+        <v>504</v>
       </c>
       <c r="N53" s="18" t="s">
-        <v>578</v>
+        <v>505</v>
       </c>
       <c r="O53" s="19">
-        <v>65115</v>
+        <v>55281</v>
       </c>
       <c r="P53" s="20" t="s">
-        <v>579</v>
+        <v>506</v>
       </c>
       <c r="Q53" s="17" t="s">
-        <v>574</v>
+        <v>501</v>
       </c>
       <c r="R53" s="22" t="s">
         <v>35</v>
       </c>
       <c r="S53" s="34">
-        <v>-7.9711650000000001</v>
+        <v>-7.8010229999999998</v>
       </c>
       <c r="T53" s="34">
-        <v>112.60970399999999</v>
+        <v>110.373188</v>
       </c>
       <c r="U53" s="24" t="s">
-        <v>53</v>
+        <v>496</v>
       </c>
       <c r="V53" s="25" t="s">
         <v>39</v>
@@ -7379,68 +8070,68 @@
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A54" s="8">
-        <v>61</v>
+      <c r="A54" s="33">
+        <v>53</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>580</v>
+        <v>507</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D54" s="32">
-        <v>30009465</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="F54" s="29" t="s">
-        <v>582</v>
+      <c r="D54" s="37">
+        <v>30011112</v>
+      </c>
+      <c r="E54" s="38" t="s">
+        <v>508</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>508</v>
       </c>
       <c r="G54" s="14">
-        <v>6002390145</v>
+        <v>6020996056</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>583</v>
+        <v>509</v>
       </c>
       <c r="I54" s="15" t="s">
-        <v>584</v>
+        <v>510</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>585</v>
+        <v>138</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>586</v>
+        <v>511</v>
       </c>
       <c r="L54" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="M54" s="17" t="s">
-        <v>588</v>
-      </c>
-      <c r="N54" s="18" t="s">
-        <v>589</v>
-      </c>
-      <c r="O54" s="19">
-        <v>30128</v>
+        <v>512</v>
+      </c>
+      <c r="M54" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="N54" s="31" t="s">
+        <v>514</v>
+      </c>
+      <c r="O54" s="32">
+        <v>25211</v>
       </c>
       <c r="P54" s="20" t="s">
-        <v>590</v>
-      </c>
-      <c r="Q54" s="17" t="s">
-        <v>591</v>
+        <v>515</v>
+      </c>
+      <c r="Q54" s="45" t="s">
+        <v>138</v>
       </c>
       <c r="R54" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="S54" s="17">
-        <v>-2.9625940000000002</v>
-      </c>
-      <c r="T54" s="17">
-        <v>104.740132</v>
+      <c r="S54" s="45">
+        <v>-0.95997399999999999</v>
+      </c>
+      <c r="T54" s="45">
+        <v>100.363501</v>
       </c>
       <c r="U54" s="24" t="s">
-        <v>592</v>
+        <v>416</v>
       </c>
       <c r="V54" s="25" t="s">
         <v>39</v>
@@ -7454,67 +8145,67 @@
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>593</v>
+        <v>516</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="27">
-        <v>30008941</v>
-      </c>
-      <c r="E55" s="106" t="s">
-        <v>594</v>
+      <c r="D55" s="32">
+        <v>30000963</v>
+      </c>
+      <c r="E55" s="35" t="s">
+        <v>517</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>595</v>
+        <v>518</v>
       </c>
       <c r="G55" s="14">
-        <v>6002389587</v>
+        <v>6002321533</v>
       </c>
       <c r="H55" s="14" t="s">
-        <v>596</v>
+        <v>517</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>597</v>
+        <v>519</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>598</v>
+        <v>520</v>
       </c>
       <c r="L55" s="16" t="s">
-        <v>599</v>
-      </c>
-      <c r="M55" s="30" t="s">
-        <v>600</v>
-      </c>
-      <c r="N55" s="31" t="s">
-        <v>601</v>
+        <v>521</v>
+      </c>
+      <c r="M55" s="70" t="s">
+        <v>522</v>
+      </c>
+      <c r="N55" s="18" t="s">
+        <v>523</v>
       </c>
       <c r="O55" s="32">
-        <v>70236</v>
-      </c>
-      <c r="P55" s="20" t="s">
-        <v>602</v>
+        <v>11250</v>
+      </c>
+      <c r="P55" s="45" t="s">
+        <v>524</v>
       </c>
       <c r="Q55" s="21" t="s">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="R55" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="S55" s="21">
-        <v>-3.320084</v>
-      </c>
-      <c r="T55" s="21">
-        <v>114.607764</v>
+        <v>35</v>
+      </c>
+      <c r="S55" s="23">
+        <v>-6.1466149999999997</v>
+      </c>
+      <c r="T55" s="23">
+        <v>106.80638399999999</v>
       </c>
       <c r="U55" s="24" t="s">
-        <v>603</v>
+        <v>53</v>
       </c>
       <c r="V55" s="25" t="s">
         <v>39</v>
@@ -7528,69 +8219,73 @@
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>604</v>
+        <v>855</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D56" s="27">
-        <v>30008290</v>
-      </c>
-      <c r="E56" s="107" t="s">
-        <v>605</v>
-      </c>
-      <c r="F56" s="108" t="s">
-        <v>606</v>
-      </c>
-      <c r="G56" s="109"/>
-      <c r="H56" s="109"/>
+      <c r="D56" s="32">
+        <v>30004500</v>
+      </c>
+      <c r="E56" s="161" t="s">
+        <v>856</v>
+      </c>
+      <c r="F56" s="161" t="s">
+        <v>857</v>
+      </c>
+      <c r="G56" s="158">
+        <v>6002341644</v>
+      </c>
+      <c r="H56" s="158" t="s">
+        <v>858</v>
+      </c>
       <c r="I56" s="15" t="s">
-        <v>607</v>
+        <v>859</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>608</v>
+        <v>383</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>609</v>
+        <v>860</v>
       </c>
       <c r="L56" s="16" t="s">
-        <v>610</v>
+        <v>861</v>
       </c>
       <c r="M56" s="70" t="s">
-        <v>611</v>
+        <v>862</v>
       </c>
       <c r="N56" s="18" t="s">
-        <v>612</v>
+        <v>863</v>
       </c>
       <c r="O56" s="32">
-        <v>59163</v>
+        <v>60284</v>
       </c>
       <c r="P56" s="20" t="s">
-        <v>613</v>
-      </c>
-      <c r="Q56" s="21" t="s">
-        <v>608</v>
+        <v>864</v>
+      </c>
+      <c r="Q56" s="17" t="s">
+        <v>383</v>
       </c>
       <c r="R56" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="S56" s="34" t="s">
-        <v>614</v>
-      </c>
-      <c r="T56" s="34" t="s">
-        <v>615</v>
+      <c r="S56" s="34">
+        <v>-7.2999340000000004</v>
+      </c>
+      <c r="T56" s="34">
+        <v>112.755827</v>
       </c>
       <c r="U56" s="24" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="V56" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W56" s="25" t="s">
-        <v>40</v>
+        <v>792</v>
       </c>
       <c r="X56" s="22" t="s">
         <v>54</v>
@@ -7598,67 +8293,63 @@
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="33">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>616</v>
+        <v>525</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D57" s="110">
-        <v>30000976</v>
-      </c>
-      <c r="E57" s="35" t="s">
-        <v>617</v>
-      </c>
-      <c r="F57" s="29" t="s">
-        <v>618</v>
-      </c>
-      <c r="G57" s="14">
-        <v>6002321637</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>617</v>
-      </c>
+      <c r="D57" s="37">
+        <v>30010995</v>
+      </c>
+      <c r="E57" s="101" t="s">
+        <v>526</v>
+      </c>
+      <c r="F57" s="101" t="s">
+        <v>527</v>
+      </c>
+      <c r="G57" s="64"/>
+      <c r="H57" s="64"/>
       <c r="I57" s="15" t="s">
-        <v>618</v>
+        <v>528</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>28</v>
+        <v>529</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>619</v>
+        <v>530</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>620</v>
-      </c>
-      <c r="M57" s="70" t="s">
-        <v>621</v>
-      </c>
-      <c r="N57" s="18" t="s">
-        <v>622</v>
-      </c>
-      <c r="O57" s="111">
-        <v>10220</v>
-      </c>
-      <c r="P57" s="20" t="s">
-        <v>623</v>
-      </c>
-      <c r="Q57" s="21" t="s">
-        <v>34</v>
+        <v>531</v>
+      </c>
+      <c r="M57" s="22" t="s">
+        <v>532</v>
+      </c>
+      <c r="N57" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="O57" s="32">
+        <v>79672</v>
+      </c>
+      <c r="P57" s="20">
+        <v>6256822888</v>
+      </c>
+      <c r="Q57" s="45" t="s">
+        <v>534</v>
       </c>
       <c r="R57" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S57" s="112">
-        <v>-6.2092330000000002</v>
-      </c>
-      <c r="T57" s="113">
-        <v>106.820239</v>
+        <v>111</v>
+      </c>
+      <c r="S57" s="102" t="s">
+        <v>535</v>
+      </c>
+      <c r="T57" s="102" t="s">
+        <v>536</v>
       </c>
       <c r="U57" s="24" t="s">
-        <v>53</v>
+        <v>537</v>
       </c>
       <c r="V57" s="25" t="s">
         <v>39</v>
@@ -7667,72 +8358,72 @@
         <v>40</v>
       </c>
       <c r="X57" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>624</v>
+        <v>538</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="114">
-        <v>30010293</v>
+      <c r="D58" s="44">
+        <v>30010744</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="F58" s="29" t="s">
-        <v>626</v>
+        <v>539</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>27</v>
       </c>
       <c r="G58" s="14">
-        <v>6002394510</v>
+        <v>6002398050</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>627</v>
+        <v>540</v>
       </c>
       <c r="I58" s="15" t="s">
-        <v>628</v>
+        <v>539</v>
       </c>
       <c r="J58" s="15" t="s">
-        <v>200</v>
+        <v>541</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="L58" s="15" t="s">
-        <v>630</v>
-      </c>
-      <c r="M58" s="22" t="s">
-        <v>631</v>
-      </c>
-      <c r="N58" s="31" t="s">
-        <v>632</v>
-      </c>
-      <c r="O58" s="37">
-        <v>20216</v>
+        <v>542</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="M58" s="103" t="s">
+        <v>544</v>
+      </c>
+      <c r="N58" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="O58" s="32">
+        <v>42162</v>
       </c>
       <c r="P58" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="Q58" s="45" t="s">
-        <v>200</v>
+        <v>546</v>
+      </c>
+      <c r="Q58" s="21" t="s">
+        <v>547</v>
       </c>
       <c r="R58" s="22" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="S58" s="21">
-        <v>3.5869879999999998</v>
+        <v>-6.1104950000000002</v>
       </c>
       <c r="T58" s="21">
-        <v>98.704890000000006</v>
-      </c>
-      <c r="U58" s="48" t="s">
-        <v>634</v>
+        <v>106.117316</v>
+      </c>
+      <c r="U58" s="24" t="s">
+        <v>548</v>
       </c>
       <c r="V58" s="25" t="s">
         <v>39</v>
@@ -7746,67 +8437,67 @@
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>635</v>
+        <v>549</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D59" s="32">
-        <v>30004371</v>
-      </c>
-      <c r="E59" s="35" t="s">
-        <v>636</v>
+      <c r="D59" s="37">
+        <v>30090385</v>
+      </c>
+      <c r="E59" s="38" t="s">
+        <v>550</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>637</v>
+        <v>550</v>
       </c>
       <c r="G59" s="14">
-        <v>6002341588</v>
+        <v>6052078391</v>
       </c>
       <c r="H59" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="I59" s="15" t="s">
-        <v>638</v>
-      </c>
-      <c r="J59" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="K59" s="15" t="s">
-        <v>640</v>
-      </c>
-      <c r="L59" s="16" t="s">
-        <v>641</v>
-      </c>
-      <c r="M59" s="70" t="s">
-        <v>642</v>
-      </c>
-      <c r="N59" s="18" t="s">
-        <v>643</v>
-      </c>
-      <c r="O59" s="32">
-        <v>46115</v>
-      </c>
-      <c r="P59" s="115" t="s">
-        <v>644</v>
-      </c>
-      <c r="Q59" s="21" t="s">
-        <v>639</v>
+        <v>551</v>
+      </c>
+      <c r="I59" s="39" t="s">
+        <v>552</v>
+      </c>
+      <c r="J59" s="39" t="s">
+        <v>553</v>
+      </c>
+      <c r="K59" s="39" t="s">
+        <v>554</v>
+      </c>
+      <c r="L59" s="40" t="s">
+        <v>555</v>
+      </c>
+      <c r="M59" s="22" t="s">
+        <v>556</v>
+      </c>
+      <c r="N59" s="31" t="s">
+        <v>557</v>
+      </c>
+      <c r="O59" s="104">
+        <v>92713</v>
+      </c>
+      <c r="P59" s="22" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q59" s="22" t="s">
+        <v>559</v>
       </c>
       <c r="R59" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S59" s="34">
-        <v>-7.3450800000000003</v>
-      </c>
-      <c r="T59" s="34">
-        <v>108.21781</v>
-      </c>
-      <c r="U59" s="48" t="s">
-        <v>603</v>
+        <v>133</v>
+      </c>
+      <c r="S59" s="74">
+        <v>-8110656</v>
+      </c>
+      <c r="T59" s="62">
+        <v>115.08747</v>
+      </c>
+      <c r="U59" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="V59" s="25" t="s">
         <v>39</v>
@@ -7815,72 +8506,72 @@
         <v>40</v>
       </c>
       <c r="X59" s="22" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
-        <v>69</v>
+      <c r="A60" s="33">
+        <v>59</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>645</v>
+        <v>560</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="116">
-        <v>30012125</v>
-      </c>
-      <c r="E60" s="117" t="s">
-        <v>646</v>
-      </c>
-      <c r="F60" s="118" t="s">
-        <v>647</v>
+      <c r="D60" s="32">
+        <v>30010548</v>
+      </c>
+      <c r="E60" s="105" t="s">
+        <v>561</v>
+      </c>
+      <c r="F60" s="29" t="s">
+        <v>562</v>
       </c>
       <c r="G60" s="14">
-        <v>6036875579</v>
+        <v>6002394912</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>647</v>
-      </c>
-      <c r="I60" s="119" t="s">
-        <v>648</v>
-      </c>
-      <c r="J60" s="119" t="s">
-        <v>649</v>
-      </c>
-      <c r="K60" s="119" t="s">
-        <v>650</v>
-      </c>
-      <c r="L60" s="120" t="s">
-        <v>651</v>
-      </c>
-      <c r="M60" s="22" t="s">
-        <v>652</v>
+        <v>563</v>
+      </c>
+      <c r="I60" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="M60" s="30" t="s">
+        <v>567</v>
       </c>
       <c r="N60" s="31" t="s">
-        <v>653</v>
-      </c>
-      <c r="O60" s="37">
-        <v>12540</v>
-      </c>
-      <c r="P60" s="25" t="s">
-        <v>654</v>
-      </c>
-      <c r="Q60" s="22" t="s">
-        <v>34</v>
+        <v>568</v>
+      </c>
+      <c r="O60" s="32">
+        <v>99111</v>
+      </c>
+      <c r="P60" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="Q60" s="21" t="s">
+        <v>564</v>
       </c>
       <c r="R60" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S60" s="45">
-        <v>-6.2794669417268096</v>
-      </c>
-      <c r="T60" s="45">
-        <v>106.833667212073</v>
-      </c>
-      <c r="U60" s="121" t="s">
-        <v>38</v>
+        <v>217</v>
+      </c>
+      <c r="S60" s="21">
+        <v>-2.5894029999999999</v>
+      </c>
+      <c r="T60" s="21">
+        <v>140.38442599999999</v>
+      </c>
+      <c r="U60" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="V60" s="25" t="s">
         <v>39</v>
@@ -7894,66 +8585,66 @@
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>655</v>
+        <v>570</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="122">
-        <v>30000974</v>
-      </c>
-      <c r="E61" s="123" t="s">
-        <v>656</v>
-      </c>
-      <c r="F61" s="124" t="s">
-        <v>656</v>
+      <c r="D61" s="11">
+        <v>30000966</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>572</v>
       </c>
       <c r="G61" s="14">
-        <v>6002321578</v>
+        <v>6002321630</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>657</v>
-      </c>
-      <c r="I61" s="119" t="s">
-        <v>658</v>
-      </c>
-      <c r="J61" s="119" t="s">
-        <v>116</v>
-      </c>
-      <c r="K61" s="119" t="s">
-        <v>659</v>
-      </c>
-      <c r="L61" s="120" t="s">
-        <v>660</v>
-      </c>
-      <c r="M61" s="30" t="s">
-        <v>661</v>
-      </c>
-      <c r="N61" s="31" t="s">
-        <v>662</v>
-      </c>
-      <c r="O61" s="55">
-        <v>14450</v>
+        <v>571</v>
+      </c>
+      <c r="I61" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="K61" s="15" t="s">
+        <v>575</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="M61" s="17" t="s">
+        <v>577</v>
+      </c>
+      <c r="N61" s="18" t="s">
+        <v>578</v>
+      </c>
+      <c r="O61" s="19">
+        <v>65115</v>
       </c>
       <c r="P61" s="20" t="s">
-        <v>663</v>
-      </c>
-      <c r="Q61" s="21" t="s">
-        <v>34</v>
+        <v>579</v>
+      </c>
+      <c r="Q61" s="17" t="s">
+        <v>574</v>
       </c>
       <c r="R61" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="S61" s="23">
-        <v>-6.1602230000000002</v>
-      </c>
-      <c r="T61" s="23">
-        <v>106.813498</v>
-      </c>
-      <c r="U61" s="48" t="s">
+      <c r="S61" s="34">
+        <v>-7.9711650000000001</v>
+      </c>
+      <c r="T61" s="34">
+        <v>112.60970399999999</v>
+      </c>
+      <c r="U61" s="24" t="s">
         <v>53</v>
       </c>
       <c r="V61" s="25" t="s">
@@ -7962,73 +8653,73 @@
       <c r="W61" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X61" s="22" t="s">
-        <v>54</v>
+      <c r="X61" s="26" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>664</v>
+        <v>580</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="11">
-        <v>30000980</v>
+      <c r="D62" s="32">
+        <v>30009465</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>665</v>
+        <v>581</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>666</v>
+        <v>582</v>
       </c>
       <c r="G62" s="14">
-        <v>6002325119</v>
+        <v>6002390145</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>667</v>
+        <v>583</v>
       </c>
       <c r="I62" s="15" t="s">
-        <v>668</v>
+        <v>584</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>669</v>
+        <v>585</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="L62" s="15" t="s">
-        <v>671</v>
+        <v>586</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>587</v>
       </c>
       <c r="M62" s="17" t="s">
-        <v>672</v>
+        <v>588</v>
       </c>
       <c r="N62" s="18" t="s">
-        <v>673</v>
+        <v>589</v>
       </c>
       <c r="O62" s="19">
-        <v>28121</v>
+        <v>30128</v>
       </c>
       <c r="P62" s="20" t="s">
-        <v>674</v>
+        <v>590</v>
       </c>
       <c r="Q62" s="17" t="s">
-        <v>675</v>
+        <v>591</v>
       </c>
       <c r="R62" s="22" t="s">
-        <v>669</v>
-      </c>
-      <c r="S62" s="34">
-        <v>0.51802400000000004</v>
-      </c>
-      <c r="T62" s="34">
-        <v>101.437862</v>
-      </c>
-      <c r="U62" s="48" t="s">
-        <v>446</v>
+        <v>64</v>
+      </c>
+      <c r="S62" s="17">
+        <v>-2.9625940000000002</v>
+      </c>
+      <c r="T62" s="17">
+        <v>104.740132</v>
+      </c>
+      <c r="U62" s="24" t="s">
+        <v>592</v>
       </c>
       <c r="V62" s="25" t="s">
         <v>39</v>
@@ -8041,142 +8732,142 @@
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A63" s="8">
-        <v>76</v>
+      <c r="A63" s="33">
+        <v>62</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>676</v>
+        <v>865</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="32">
-        <v>30009876</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>677</v>
-      </c>
-      <c r="F63" s="29" t="s">
-        <v>678</v>
-      </c>
-      <c r="G63" s="14">
-        <v>6002394133</v>
-      </c>
-      <c r="H63" s="14" t="s">
-        <v>679</v>
-      </c>
-      <c r="I63" s="15" t="s">
-        <v>680</v>
-      </c>
-      <c r="J63" s="15" t="s">
-        <v>681</v>
-      </c>
-      <c r="K63" s="15" t="s">
-        <v>682</v>
-      </c>
-      <c r="L63" s="16" t="s">
-        <v>683</v>
-      </c>
-      <c r="M63" s="17" t="s">
-        <v>684</v>
-      </c>
-      <c r="N63" s="18" t="s">
-        <v>685</v>
-      </c>
-      <c r="O63" s="19">
-        <v>57135</v>
-      </c>
-      <c r="P63" s="20" t="s">
-        <v>686</v>
-      </c>
-      <c r="Q63" s="17" t="s">
-        <v>681</v>
+      <c r="D63" s="153">
+        <v>30076785</v>
+      </c>
+      <c r="E63" s="168" t="s">
+        <v>866</v>
+      </c>
+      <c r="F63" s="157" t="s">
+        <v>867</v>
+      </c>
+      <c r="G63" s="158">
+        <v>6048562974</v>
+      </c>
+      <c r="H63" s="158" t="s">
+        <v>868</v>
+      </c>
+      <c r="I63" s="39" t="s">
+        <v>869</v>
+      </c>
+      <c r="J63" s="39" t="s">
+        <v>364</v>
+      </c>
+      <c r="K63" s="39" t="s">
+        <v>870</v>
+      </c>
+      <c r="L63" s="40" t="s">
+        <v>871</v>
+      </c>
+      <c r="M63" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="N63" s="31" t="s">
+        <v>873</v>
+      </c>
+      <c r="O63" s="61">
+        <v>41311</v>
+      </c>
+      <c r="P63" s="84" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q63" s="22" t="s">
+        <v>364</v>
       </c>
       <c r="R63" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S63" s="17">
-        <v>110.82391200000001</v>
-      </c>
-      <c r="T63" s="17">
-        <v>-7.5507350000000004</v>
-      </c>
-      <c r="U63" s="48" t="s">
-        <v>687</v>
+        <v>173</v>
+      </c>
+      <c r="S63" s="62">
+        <v>-6.30154937</v>
+      </c>
+      <c r="T63" s="62">
+        <v>107.2948926</v>
+      </c>
+      <c r="U63" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="V63" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W63" s="25" t="s">
-        <v>40</v>
+        <v>792</v>
       </c>
       <c r="X63" s="22" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A64" s="33">
-        <v>77</v>
+      <c r="A64" s="8">
+        <v>63</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>688</v>
+        <v>593</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D64" s="37">
-        <v>30068257</v>
-      </c>
-      <c r="E64" s="125" t="s">
-        <v>689</v>
-      </c>
-      <c r="F64" s="125" t="s">
-        <v>690</v>
+      <c r="D64" s="27">
+        <v>30008941</v>
+      </c>
+      <c r="E64" s="106" t="s">
+        <v>594</v>
+      </c>
+      <c r="F64" s="29" t="s">
+        <v>595</v>
       </c>
       <c r="G64" s="14">
-        <v>6041986664</v>
+        <v>6002389587</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>691</v>
-      </c>
-      <c r="I64" s="126" t="s">
-        <v>689</v>
-      </c>
-      <c r="J64" s="126" t="s">
-        <v>364</v>
-      </c>
-      <c r="K64" s="126" t="s">
-        <v>692</v>
-      </c>
-      <c r="L64" s="127" t="s">
-        <v>693</v>
-      </c>
-      <c r="M64" s="22" t="s">
-        <v>694</v>
+        <v>596</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>597</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>599</v>
+      </c>
+      <c r="M64" s="30" t="s">
+        <v>600</v>
       </c>
       <c r="N64" s="31" t="s">
-        <v>695</v>
-      </c>
-      <c r="O64" s="37">
-        <v>41312</v>
-      </c>
-      <c r="P64" s="128" t="s">
-        <v>696</v>
-      </c>
-      <c r="Q64" s="22" t="s">
-        <v>364</v>
+        <v>601</v>
+      </c>
+      <c r="O64" s="32">
+        <v>70236</v>
+      </c>
+      <c r="P64" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q64" s="21" t="s">
+        <v>331</v>
       </c>
       <c r="R64" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="S64" s="45">
-        <v>-6.3048099999999998</v>
-      </c>
-      <c r="T64" s="45">
-        <v>107.298988820902</v>
-      </c>
-      <c r="U64" s="121" t="s">
-        <v>38</v>
+        <v>111</v>
+      </c>
+      <c r="S64" s="21">
+        <v>-3.320084</v>
+      </c>
+      <c r="T64" s="21">
+        <v>114.607764</v>
+      </c>
+      <c r="U64" s="24" t="s">
+        <v>603</v>
       </c>
       <c r="V64" s="25" t="s">
         <v>39</v>
@@ -8184,73 +8875,69 @@
       <c r="W64" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X64" s="22" t="s">
+      <c r="X64" s="26" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>697</v>
+        <v>604</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D65" s="50">
-        <v>30009222</v>
-      </c>
-      <c r="E65" s="28" t="s">
-        <v>698</v>
-      </c>
-      <c r="F65" s="29" t="s">
-        <v>699</v>
-      </c>
-      <c r="G65" s="14">
-        <v>6002390277</v>
-      </c>
-      <c r="H65" s="14" t="s">
-        <v>700</v>
-      </c>
+      <c r="D65" s="27">
+        <v>30008290</v>
+      </c>
+      <c r="E65" s="107" t="s">
+        <v>605</v>
+      </c>
+      <c r="F65" s="108" t="s">
+        <v>606</v>
+      </c>
+      <c r="G65" s="109"/>
+      <c r="H65" s="109"/>
       <c r="I65" s="15" t="s">
-        <v>701</v>
+        <v>607</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>702</v>
+        <v>608</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>703</v>
+        <v>609</v>
       </c>
       <c r="L65" s="16" t="s">
-        <v>704</v>
-      </c>
-      <c r="M65" s="30" t="s">
-        <v>705</v>
-      </c>
-      <c r="N65" s="31" t="s">
-        <v>706</v>
+        <v>610</v>
+      </c>
+      <c r="M65" s="70" t="s">
+        <v>611</v>
+      </c>
+      <c r="N65" s="18" t="s">
+        <v>612</v>
       </c>
       <c r="O65" s="32">
-        <v>96111</v>
+        <v>59163</v>
       </c>
       <c r="P65" s="20" t="s">
-        <v>707</v>
+        <v>613</v>
       </c>
       <c r="Q65" s="21" t="s">
-        <v>702</v>
+        <v>608</v>
       </c>
       <c r="R65" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="S65" s="21">
-        <v>0.53542400000000001</v>
-      </c>
-      <c r="T65" s="21">
-        <v>123.05843</v>
-      </c>
-      <c r="U65" s="48" t="s">
-        <v>53</v>
+        <v>35</v>
+      </c>
+      <c r="S65" s="34" t="s">
+        <v>614</v>
+      </c>
+      <c r="T65" s="34" t="s">
+        <v>615</v>
+      </c>
+      <c r="U65" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="V65" s="25" t="s">
         <v>39</v>
@@ -8259,72 +8946,72 @@
         <v>40</v>
       </c>
       <c r="X65" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:24" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="33">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>708</v>
+        <v>616</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D66" s="32">
-        <v>30008461</v>
+      <c r="D66" s="110">
+        <v>30000976</v>
       </c>
       <c r="E66" s="35" t="s">
-        <v>709</v>
+        <v>617</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>710</v>
+        <v>618</v>
       </c>
       <c r="G66" s="14">
-        <v>6002359466</v>
+        <v>6002321637</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>711</v>
+        <v>617</v>
       </c>
       <c r="I66" s="15" t="s">
-        <v>712</v>
+        <v>618</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>713</v>
+        <v>619</v>
       </c>
       <c r="L66" s="16" t="s">
-        <v>714</v>
-      </c>
-      <c r="M66" s="129" t="s">
-        <v>715</v>
-      </c>
-      <c r="N66" s="130" t="s">
-        <v>716</v>
-      </c>
-      <c r="O66" s="131">
-        <v>78122</v>
-      </c>
-      <c r="P66" s="132">
-        <v>6285157870590</v>
-      </c>
-      <c r="Q66" s="133" t="s">
-        <v>188</v>
-      </c>
-      <c r="R66" s="128" t="s">
-        <v>111</v>
-      </c>
-      <c r="S66" s="34">
-        <v>-5.04E-2</v>
-      </c>
-      <c r="T66" s="34">
-        <v>109.344667</v>
-      </c>
-      <c r="U66" s="48" t="s">
-        <v>717</v>
+        <v>620</v>
+      </c>
+      <c r="M66" s="70" t="s">
+        <v>621</v>
+      </c>
+      <c r="N66" s="18" t="s">
+        <v>622</v>
+      </c>
+      <c r="O66" s="111">
+        <v>10220</v>
+      </c>
+      <c r="P66" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q66" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="R66" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="S66" s="112">
+        <v>-6.2092330000000002</v>
+      </c>
+      <c r="T66" s="113">
+        <v>106.820239</v>
+      </c>
+      <c r="U66" s="24" t="s">
+        <v>53</v>
       </c>
       <c r="V66" s="25" t="s">
         <v>39</v>
@@ -8338,67 +9025,67 @@
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>718</v>
+        <v>624</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D67" s="134">
-        <v>30076364</v>
-      </c>
-      <c r="E67" s="135" t="s">
-        <v>719</v>
+      <c r="D67" s="114">
+        <v>30010293</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>625</v>
       </c>
       <c r="F67" s="29" t="s">
-        <v>720</v>
+        <v>626</v>
       </c>
       <c r="G67" s="14">
-        <v>6046148081</v>
+        <v>6002394510</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>719</v>
-      </c>
-      <c r="I67" s="136" t="s">
-        <v>721</v>
-      </c>
-      <c r="J67" s="136" t="s">
-        <v>722</v>
-      </c>
-      <c r="K67" s="136" t="s">
-        <v>723</v>
-      </c>
-      <c r="L67" s="137" t="s">
-        <v>724</v>
-      </c>
-      <c r="M67" s="138" t="s">
-        <v>725</v>
-      </c>
-      <c r="N67" s="139" t="s">
-        <v>726</v>
-      </c>
-      <c r="O67" s="140">
-        <v>98414</v>
-      </c>
-      <c r="P67" s="141" t="s">
-        <v>727</v>
-      </c>
-      <c r="Q67" s="22" t="s">
-        <v>728</v>
+        <v>627</v>
+      </c>
+      <c r="I67" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="K67" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="L67" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="M67" s="22" t="s">
+        <v>631</v>
+      </c>
+      <c r="N67" s="31" t="s">
+        <v>632</v>
+      </c>
+      <c r="O67" s="37">
+        <v>20216</v>
+      </c>
+      <c r="P67" s="20" t="s">
+        <v>633</v>
+      </c>
+      <c r="Q67" s="45" t="s">
+        <v>200</v>
       </c>
       <c r="R67" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="S67" s="141">
-        <v>-0.88283449999999997</v>
-      </c>
-      <c r="T67" s="141">
-        <v>131.2833895</v>
-      </c>
-      <c r="U67" s="142" t="s">
-        <v>38</v>
+        <v>64</v>
+      </c>
+      <c r="S67" s="21">
+        <v>3.5869879999999998</v>
+      </c>
+      <c r="T67" s="21">
+        <v>98.704890000000006</v>
+      </c>
+      <c r="U67" s="48" t="s">
+        <v>634</v>
       </c>
       <c r="V67" s="25" t="s">
         <v>39</v>
@@ -8406,73 +9093,73 @@
       <c r="W67" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X67" s="138" t="s">
-        <v>89</v>
+      <c r="X67" s="22" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>729</v>
+        <v>635</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D68" s="11">
-        <v>30000982</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>730</v>
+      <c r="D68" s="32">
+        <v>30004371</v>
+      </c>
+      <c r="E68" s="35" t="s">
+        <v>636</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>731</v>
+        <v>637</v>
       </c>
       <c r="G68" s="14">
-        <v>6002325123</v>
+        <v>6002341588</v>
       </c>
       <c r="H68" s="14" t="s">
-        <v>732</v>
+        <v>636</v>
       </c>
       <c r="I68" s="15" t="s">
-        <v>733</v>
+        <v>638</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>432</v>
+        <v>639</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>734</v>
-      </c>
-      <c r="L68" s="143" t="s">
-        <v>735</v>
-      </c>
-      <c r="M68" s="17" t="s">
-        <v>736</v>
+        <v>640</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="M68" s="70" t="s">
+        <v>642</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>737</v>
-      </c>
-      <c r="O68" s="19">
-        <v>80237</v>
-      </c>
-      <c r="P68" s="20" t="s">
-        <v>738</v>
-      </c>
-      <c r="Q68" s="17" t="s">
-        <v>432</v>
+        <v>643</v>
+      </c>
+      <c r="O68" s="32">
+        <v>46115</v>
+      </c>
+      <c r="P68" s="115" t="s">
+        <v>644</v>
+      </c>
+      <c r="Q68" s="21" t="s">
+        <v>639</v>
       </c>
       <c r="R68" s="22" t="s">
-        <v>320</v>
+        <v>35</v>
       </c>
       <c r="S68" s="34">
-        <v>-8.6418359999999996</v>
+        <v>-7.3450800000000003</v>
       </c>
       <c r="T68" s="34">
-        <v>115.234284</v>
+        <v>108.21781</v>
       </c>
       <c r="U68" s="48" t="s">
-        <v>53</v>
+        <v>603</v>
       </c>
       <c r="V68" s="25" t="s">
         <v>39</v>
@@ -8481,143 +9168,139 @@
         <v>40</v>
       </c>
       <c r="X68" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A69" s="8">
-        <v>85</v>
+      <c r="A69" s="33">
+        <v>68</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>739</v>
+        <v>875</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D69" s="144">
-        <v>30011151</v>
-      </c>
-      <c r="E69" s="135" t="s">
-        <v>740</v>
-      </c>
-      <c r="F69" s="29" t="s">
-        <v>741</v>
-      </c>
-      <c r="G69" s="14">
-        <v>6020996226</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>742</v>
-      </c>
-      <c r="I69" s="145" t="s">
-        <v>743</v>
-      </c>
-      <c r="J69" s="145" t="s">
-        <v>409</v>
-      </c>
-      <c r="K69" s="145" t="s">
-        <v>744</v>
-      </c>
-      <c r="L69" s="16" t="s">
-        <v>745</v>
-      </c>
-      <c r="M69" s="146" t="s">
-        <v>746</v>
-      </c>
-      <c r="N69" s="147" t="s">
-        <v>747</v>
-      </c>
-      <c r="O69" s="148">
-        <v>84117</v>
-      </c>
-      <c r="P69" s="149" t="s">
-        <v>748</v>
-      </c>
-      <c r="Q69" s="150" t="s">
-        <v>749</v>
-      </c>
-      <c r="R69" s="146" t="s">
-        <v>409</v>
-      </c>
-      <c r="S69" s="151">
-        <v>-8.4565239999999999</v>
-      </c>
-      <c r="T69" s="150">
-        <v>118.73248599999999</v>
-      </c>
-      <c r="U69" s="152" t="s">
-        <v>750</v>
+      <c r="D69" s="116">
+        <v>30012119</v>
+      </c>
+      <c r="E69" s="174" t="s">
+        <v>876</v>
+      </c>
+      <c r="F69" s="175" t="s">
+        <v>647</v>
+      </c>
+      <c r="G69" s="175"/>
+      <c r="H69" s="175"/>
+      <c r="I69" s="119" t="s">
+        <v>647</v>
+      </c>
+      <c r="J69" s="176" t="s">
+        <v>158</v>
+      </c>
+      <c r="K69" s="176" t="s">
+        <v>877</v>
+      </c>
+      <c r="L69" s="177" t="s">
+        <v>878</v>
+      </c>
+      <c r="M69" s="178" t="s">
+        <v>879</v>
+      </c>
+      <c r="N69" s="179" t="s">
+        <v>880</v>
+      </c>
+      <c r="O69" s="180">
+        <v>40112</v>
+      </c>
+      <c r="P69" s="178" t="s">
+        <v>881</v>
+      </c>
+      <c r="Q69" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="R69" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="S69" s="45">
+        <v>-6.9181702313327396</v>
+      </c>
+      <c r="T69" s="181">
+        <v>107.62051647742101</v>
+      </c>
+      <c r="U69" s="121" t="s">
+        <v>38</v>
       </c>
       <c r="V69" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W69" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="X69" s="146" t="s">
+        <v>792</v>
+      </c>
+      <c r="X69" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A70" s="33">
-        <v>86</v>
+      <c r="A70" s="8">
+        <v>69</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>751</v>
+        <v>645</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="153">
-        <v>30076794</v>
-      </c>
-      <c r="E70" s="29" t="s">
-        <v>752</v>
-      </c>
-      <c r="F70" s="101" t="s">
-        <v>752</v>
+      <c r="D70" s="116">
+        <v>30012125</v>
+      </c>
+      <c r="E70" s="117" t="s">
+        <v>646</v>
+      </c>
+      <c r="F70" s="118" t="s">
+        <v>647</v>
       </c>
       <c r="G70" s="14">
-        <v>6048719838</v>
+        <v>6036875579</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>752</v>
-      </c>
-      <c r="I70" s="39" t="s">
-        <v>753</v>
-      </c>
-      <c r="J70" s="39" t="s">
-        <v>501</v>
-      </c>
-      <c r="K70" s="39" t="s">
-        <v>754</v>
-      </c>
-      <c r="L70" s="40" t="s">
-        <v>755</v>
+        <v>647</v>
+      </c>
+      <c r="I70" s="119" t="s">
+        <v>648</v>
+      </c>
+      <c r="J70" s="119" t="s">
+        <v>649</v>
+      </c>
+      <c r="K70" s="119" t="s">
+        <v>650</v>
+      </c>
+      <c r="L70" s="120" t="s">
+        <v>651</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>756</v>
+        <v>652</v>
       </c>
       <c r="N70" s="31" t="s">
-        <v>757</v>
-      </c>
-      <c r="O70" s="61">
-        <v>55121</v>
-      </c>
-      <c r="P70" s="154" t="s">
-        <v>758</v>
-      </c>
-      <c r="Q70" s="26" t="s">
-        <v>759</v>
-      </c>
-      <c r="R70" s="26" t="s">
-        <v>760</v>
-      </c>
-      <c r="S70" s="62">
-        <v>-7.8058531410279901</v>
-      </c>
-      <c r="T70" s="62">
-        <v>110.36974667600001</v>
+        <v>653</v>
+      </c>
+      <c r="O70" s="37">
+        <v>12540</v>
+      </c>
+      <c r="P70" s="25" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q70" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="R70" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="S70" s="45">
+        <v>-6.2794669417268096</v>
+      </c>
+      <c r="T70" s="45">
+        <v>106.833667212073</v>
       </c>
       <c r="U70" s="121" t="s">
         <v>38</v>
@@ -8629,217 +9312,1491 @@
         <v>40</v>
       </c>
       <c r="X70" s="22" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>761</v>
+        <v>882</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="153"/>
-      <c r="E71" s="80" t="s">
-        <v>762</v>
-      </c>
-      <c r="F71" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="G71" s="14">
-        <v>6032066339</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>764</v>
-      </c>
+      <c r="D71" s="116">
+        <v>30012118</v>
+      </c>
+      <c r="E71" s="174" t="s">
+        <v>883</v>
+      </c>
+      <c r="F71" s="175" t="s">
+        <v>647</v>
+      </c>
+      <c r="G71" s="175"/>
+      <c r="H71" s="175"/>
       <c r="I71" s="15" t="s">
-        <v>765</v>
+        <v>648</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>766</v>
+        <v>383</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>767</v>
+        <v>884</v>
       </c>
       <c r="L71" s="16" t="s">
-        <v>768</v>
-      </c>
-      <c r="M71" s="155" t="s">
-        <v>769</v>
+        <v>885</v>
+      </c>
+      <c r="M71" s="22" t="s">
+        <v>886</v>
       </c>
       <c r="N71" s="31" t="s">
-        <v>770</v>
-      </c>
-      <c r="O71" s="155"/>
-      <c r="P71" s="155"/>
-      <c r="Q71" s="155"/>
-      <c r="R71" s="155"/>
-      <c r="S71" s="155"/>
-      <c r="T71" s="155"/>
-      <c r="U71" s="155"/>
+        <v>887</v>
+      </c>
+      <c r="O71" s="37">
+        <v>60118</v>
+      </c>
+      <c r="P71" s="25" t="s">
+        <v>888</v>
+      </c>
+      <c r="Q71" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="R71" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="S71" s="45">
+        <v>7.2994408301373399</v>
+      </c>
+      <c r="T71" s="45">
+        <v>112.770680085655</v>
+      </c>
+      <c r="U71" s="121" t="s">
+        <v>38</v>
+      </c>
       <c r="V71" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W71" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="X71" s="155"/>
+        <v>792</v>
+      </c>
+      <c r="X71" s="22" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A72" s="8">
-        <v>88</v>
+      <c r="A72" s="33">
+        <v>71</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>771</v>
+        <v>889</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="153"/>
-      <c r="E72" s="80" t="s">
-        <v>772</v>
-      </c>
-      <c r="F72" s="29" t="s">
-        <v>773</v>
-      </c>
-      <c r="G72" s="14">
-        <v>6060304421</v>
-      </c>
-      <c r="H72" s="14" t="s">
-        <v>774</v>
-      </c>
-      <c r="I72" s="52" t="s">
-        <v>775</v>
-      </c>
-      <c r="J72" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="K72" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="L72" s="53" t="s">
-        <v>777</v>
-      </c>
-      <c r="M72" s="155" t="s">
-        <v>778</v>
+      <c r="D72" s="37">
+        <v>30036839</v>
+      </c>
+      <c r="E72" s="168" t="s">
+        <v>890</v>
+      </c>
+      <c r="F72" s="169" t="s">
+        <v>890</v>
+      </c>
+      <c r="G72" s="169"/>
+      <c r="H72" s="169"/>
+      <c r="I72" s="15" t="s">
+        <v>891</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>892</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>893</v>
+      </c>
+      <c r="M72" s="22" t="s">
+        <v>894</v>
       </c>
       <c r="N72" s="31" t="s">
-        <v>779</v>
-      </c>
-      <c r="O72" s="155"/>
-      <c r="P72" s="155"/>
-      <c r="Q72" s="155"/>
-      <c r="R72" s="155"/>
-      <c r="S72" s="155"/>
-      <c r="T72" s="155"/>
-      <c r="U72" s="155"/>
+        <v>895</v>
+      </c>
+      <c r="O72" s="104">
+        <v>80238</v>
+      </c>
+      <c r="P72" s="45">
+        <v>81584603865</v>
+      </c>
+      <c r="Q72" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="R72" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="S72" s="45">
+        <v>-8.6727574000000001</v>
+      </c>
+      <c r="T72" s="45">
+        <v>115.22383120000001</v>
+      </c>
+      <c r="U72" s="121" t="s">
+        <v>38</v>
+      </c>
       <c r="V72" s="25" t="s">
         <v>39</v>
       </c>
       <c r="W72" s="25" t="s">
+        <v>792</v>
+      </c>
+      <c r="X72" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>72</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" s="122">
+        <v>30000974</v>
+      </c>
+      <c r="E73" s="123" t="s">
+        <v>656</v>
+      </c>
+      <c r="F73" s="124" t="s">
+        <v>656</v>
+      </c>
+      <c r="G73" s="14">
+        <v>6002321578</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>657</v>
+      </c>
+      <c r="I73" s="119" t="s">
+        <v>658</v>
+      </c>
+      <c r="J73" s="119" t="s">
+        <v>116</v>
+      </c>
+      <c r="K73" s="119" t="s">
+        <v>659</v>
+      </c>
+      <c r="L73" s="120" t="s">
+        <v>660</v>
+      </c>
+      <c r="M73" s="30" t="s">
+        <v>661</v>
+      </c>
+      <c r="N73" s="31" t="s">
+        <v>662</v>
+      </c>
+      <c r="O73" s="55">
+        <v>14450</v>
+      </c>
+      <c r="P73" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q73" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="R73" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="S73" s="23">
+        <v>-6.1602230000000002</v>
+      </c>
+      <c r="T73" s="23">
+        <v>106.813498</v>
+      </c>
+      <c r="U73" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="V73" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W73" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="X72" s="155"/>
+      <c r="X73" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>73</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="153">
+        <v>30076374</v>
+      </c>
+      <c r="E74" s="182" t="s">
+        <v>897</v>
+      </c>
+      <c r="F74" s="183" t="s">
+        <v>897</v>
+      </c>
+      <c r="G74" s="184">
+        <v>6046500541</v>
+      </c>
+      <c r="H74" s="184" t="s">
+        <v>898</v>
+      </c>
+      <c r="I74" s="39" t="s">
+        <v>899</v>
+      </c>
+      <c r="J74" s="39" t="s">
+        <v>900</v>
+      </c>
+      <c r="K74" s="39" t="s">
+        <v>901</v>
+      </c>
+      <c r="L74" s="40" t="s">
+        <v>902</v>
+      </c>
+      <c r="M74" s="22" t="s">
+        <v>903</v>
+      </c>
+      <c r="N74" s="31" t="s">
+        <v>904</v>
+      </c>
+      <c r="O74" s="37">
+        <v>94111</v>
+      </c>
+      <c r="P74" s="45" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q74" s="22" t="s">
+        <v>900</v>
+      </c>
+      <c r="R74" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="S74" s="45">
+        <v>-0.88857900000000001</v>
+      </c>
+      <c r="T74" s="45">
+        <v>119.879031</v>
+      </c>
+      <c r="U74" s="121" t="s">
+        <v>906</v>
+      </c>
+      <c r="V74" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W74" s="25" t="s">
+        <v>792</v>
+      </c>
+      <c r="X74" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A75" s="33">
+        <v>74</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" s="44">
+        <v>30039098</v>
+      </c>
+      <c r="E75" s="174" t="s">
+        <v>908</v>
+      </c>
+      <c r="F75" s="157" t="s">
+        <v>908</v>
+      </c>
+      <c r="G75" s="184">
+        <v>6040581181</v>
+      </c>
+      <c r="H75" s="184" t="s">
+        <v>909</v>
+      </c>
+      <c r="I75" s="15" t="s">
+        <v>910</v>
+      </c>
+      <c r="J75" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>911</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>912</v>
+      </c>
+      <c r="M75" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="N75" s="31" t="s">
+        <v>914</v>
+      </c>
+      <c r="O75" s="37">
+        <v>70234</v>
+      </c>
+      <c r="P75" s="22" t="s">
+        <v>915</v>
+      </c>
+      <c r="Q75" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="R75" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="S75" s="45">
+        <v>-3.327699</v>
+      </c>
+      <c r="T75" s="45">
+        <v>114607482</v>
+      </c>
+      <c r="U75" s="121" t="s">
+        <v>38</v>
+      </c>
+      <c r="V75" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W75" s="25" t="s">
+        <v>792</v>
+      </c>
+      <c r="X75" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <v>75</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="11">
+        <v>30000980</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="F76" s="29" t="s">
+        <v>666</v>
+      </c>
+      <c r="G76" s="14">
+        <v>6002325119</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>667</v>
+      </c>
+      <c r="I76" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="J76" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="K76" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="L76" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="M76" s="17" t="s">
+        <v>672</v>
+      </c>
+      <c r="N76" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="O76" s="19">
+        <v>28121</v>
+      </c>
+      <c r="P76" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="Q76" s="17" t="s">
+        <v>675</v>
+      </c>
+      <c r="R76" s="22" t="s">
+        <v>669</v>
+      </c>
+      <c r="S76" s="34">
+        <v>0.51802400000000004</v>
+      </c>
+      <c r="T76" s="34">
+        <v>101.437862</v>
+      </c>
+      <c r="U76" s="48" t="s">
+        <v>446</v>
+      </c>
+      <c r="V76" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W76" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X76" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <v>76</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" s="32">
+        <v>30009876</v>
+      </c>
+      <c r="E77" s="28" t="s">
+        <v>677</v>
+      </c>
+      <c r="F77" s="29" t="s">
+        <v>678</v>
+      </c>
+      <c r="G77" s="14">
+        <v>6002394133</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>679</v>
+      </c>
+      <c r="I77" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="J77" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="K77" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="M77" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="N77" s="18" t="s">
+        <v>685</v>
+      </c>
+      <c r="O77" s="19">
+        <v>57135</v>
+      </c>
+      <c r="P77" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="Q77" s="17" t="s">
+        <v>681</v>
+      </c>
+      <c r="R77" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="S77" s="17">
+        <v>110.82391200000001</v>
+      </c>
+      <c r="T77" s="17">
+        <v>-7.5507350000000004</v>
+      </c>
+      <c r="U77" s="48" t="s">
+        <v>687</v>
+      </c>
+      <c r="V77" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W77" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X77" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A78" s="33">
+        <v>77</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="37">
+        <v>30068257</v>
+      </c>
+      <c r="E78" s="125" t="s">
+        <v>689</v>
+      </c>
+      <c r="F78" s="125" t="s">
+        <v>690</v>
+      </c>
+      <c r="G78" s="14">
+        <v>6041986664</v>
+      </c>
+      <c r="H78" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="I78" s="126" t="s">
+        <v>689</v>
+      </c>
+      <c r="J78" s="126" t="s">
+        <v>364</v>
+      </c>
+      <c r="K78" s="126" t="s">
+        <v>692</v>
+      </c>
+      <c r="L78" s="127" t="s">
+        <v>693</v>
+      </c>
+      <c r="M78" s="22" t="s">
+        <v>694</v>
+      </c>
+      <c r="N78" s="31" t="s">
+        <v>695</v>
+      </c>
+      <c r="O78" s="37">
+        <v>41312</v>
+      </c>
+      <c r="P78" s="128" t="s">
+        <v>696</v>
+      </c>
+      <c r="Q78" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="R78" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="S78" s="45">
+        <v>-6.3048099999999998</v>
+      </c>
+      <c r="T78" s="45">
+        <v>107.298988820902</v>
+      </c>
+      <c r="U78" s="121" t="s">
+        <v>38</v>
+      </c>
+      <c r="V78" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W78" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X78" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A79" s="8">
+        <v>78</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" s="50">
+        <v>30009222</v>
+      </c>
+      <c r="E79" s="28" t="s">
+        <v>698</v>
+      </c>
+      <c r="F79" s="29" t="s">
+        <v>699</v>
+      </c>
+      <c r="G79" s="14">
+        <v>6002390277</v>
+      </c>
+      <c r="H79" s="14" t="s">
+        <v>700</v>
+      </c>
+      <c r="I79" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="K79" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>704</v>
+      </c>
+      <c r="M79" s="30" t="s">
+        <v>705</v>
+      </c>
+      <c r="N79" s="31" t="s">
+        <v>706</v>
+      </c>
+      <c r="O79" s="32">
+        <v>96111</v>
+      </c>
+      <c r="P79" s="20" t="s">
+        <v>707</v>
+      </c>
+      <c r="Q79" s="21" t="s">
+        <v>702</v>
+      </c>
+      <c r="R79" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="S79" s="21">
+        <v>0.53542400000000001</v>
+      </c>
+      <c r="T79" s="21">
+        <v>123.05843</v>
+      </c>
+      <c r="U79" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="V79" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W79" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X79" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <v>79</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" s="32">
+        <v>30006511</v>
+      </c>
+      <c r="E80" s="161" t="s">
+        <v>917</v>
+      </c>
+      <c r="F80" s="161"/>
+      <c r="G80" s="158">
+        <v>6002350587</v>
+      </c>
+      <c r="H80" s="158" t="s">
+        <v>917</v>
+      </c>
+      <c r="I80" s="15" t="s">
+        <v>917</v>
+      </c>
+      <c r="J80" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>918</v>
+      </c>
+      <c r="L80" s="15" t="s">
+        <v>919</v>
+      </c>
+      <c r="M80" s="70" t="s">
+        <v>920</v>
+      </c>
+      <c r="N80" s="130" t="s">
+        <v>921</v>
+      </c>
+      <c r="O80" s="131">
+        <v>28282</v>
+      </c>
+      <c r="P80" s="20">
+        <v>82169079475</v>
+      </c>
+      <c r="Q80" s="133" t="s">
+        <v>675</v>
+      </c>
+      <c r="R80" s="22" t="s">
+        <v>669</v>
+      </c>
+      <c r="S80" s="34">
+        <v>0.50831499999999996</v>
+      </c>
+      <c r="T80" s="34">
+        <v>101.442387</v>
+      </c>
+      <c r="U80" s="48" t="s">
+        <v>446</v>
+      </c>
+      <c r="V80" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W80" s="25" t="s">
+        <v>792</v>
+      </c>
+      <c r="X80" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="33">
+        <v>80</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" s="32">
+        <v>30008461</v>
+      </c>
+      <c r="E81" s="35" t="s">
+        <v>709</v>
+      </c>
+      <c r="F81" s="29" t="s">
+        <v>710</v>
+      </c>
+      <c r="G81" s="14">
+        <v>6002359466</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>711</v>
+      </c>
+      <c r="I81" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="J81" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>713</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>714</v>
+      </c>
+      <c r="M81" s="129" t="s">
+        <v>715</v>
+      </c>
+      <c r="N81" s="130" t="s">
+        <v>716</v>
+      </c>
+      <c r="O81" s="131">
+        <v>78122</v>
+      </c>
+      <c r="P81" s="132">
+        <v>6285157870590</v>
+      </c>
+      <c r="Q81" s="133" t="s">
+        <v>188</v>
+      </c>
+      <c r="R81" s="128" t="s">
+        <v>111</v>
+      </c>
+      <c r="S81" s="34">
+        <v>-5.04E-2</v>
+      </c>
+      <c r="T81" s="34">
+        <v>109.344667</v>
+      </c>
+      <c r="U81" s="48" t="s">
+        <v>717</v>
+      </c>
+      <c r="V81" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W81" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X81" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>81</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82" s="134">
+        <v>30076364</v>
+      </c>
+      <c r="E82" s="135" t="s">
+        <v>719</v>
+      </c>
+      <c r="F82" s="29" t="s">
+        <v>720</v>
+      </c>
+      <c r="G82" s="14">
+        <v>6046148081</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>719</v>
+      </c>
+      <c r="I82" s="136" t="s">
+        <v>721</v>
+      </c>
+      <c r="J82" s="136" t="s">
+        <v>722</v>
+      </c>
+      <c r="K82" s="136" t="s">
+        <v>723</v>
+      </c>
+      <c r="L82" s="137" t="s">
+        <v>724</v>
+      </c>
+      <c r="M82" s="138" t="s">
+        <v>725</v>
+      </c>
+      <c r="N82" s="139" t="s">
+        <v>726</v>
+      </c>
+      <c r="O82" s="140">
+        <v>98414</v>
+      </c>
+      <c r="P82" s="141" t="s">
+        <v>727</v>
+      </c>
+      <c r="Q82" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="R82" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="S82" s="141">
+        <v>-0.88283449999999997</v>
+      </c>
+      <c r="T82" s="141">
+        <v>131.2833895</v>
+      </c>
+      <c r="U82" s="142" t="s">
+        <v>38</v>
+      </c>
+      <c r="V82" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W82" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X82" s="138" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <v>82</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D83" s="32">
+        <v>30008914</v>
+      </c>
+      <c r="E83" s="156" t="s">
+        <v>923</v>
+      </c>
+      <c r="F83" s="157" t="s">
+        <v>924</v>
+      </c>
+      <c r="G83" s="158">
+        <v>6002389702</v>
+      </c>
+      <c r="H83" s="158" t="s">
+        <v>925</v>
+      </c>
+      <c r="I83" s="15" t="s">
+        <v>926</v>
+      </c>
+      <c r="J83" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="K83" s="15" t="s">
+        <v>927</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>928</v>
+      </c>
+      <c r="M83" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="N83" s="31" t="s">
+        <v>930</v>
+      </c>
+      <c r="O83" s="32">
+        <v>25133</v>
+      </c>
+      <c r="P83" s="20" t="s">
+        <v>931</v>
+      </c>
+      <c r="Q83" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="R83" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="S83" s="21">
+        <v>-0.94090799999999997</v>
+      </c>
+      <c r="T83" s="21">
+        <v>100.354641</v>
+      </c>
+      <c r="U83" s="48" t="s">
+        <v>446</v>
+      </c>
+      <c r="V83" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W83" s="25" t="s">
+        <v>792</v>
+      </c>
+      <c r="X83" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A84" s="33">
+        <v>83</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>932</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" s="32">
+        <v>30008368</v>
+      </c>
+      <c r="E84" s="161" t="s">
+        <v>933</v>
+      </c>
+      <c r="F84" s="157" t="s">
+        <v>934</v>
+      </c>
+      <c r="G84" s="158">
+        <v>6002359460</v>
+      </c>
+      <c r="H84" s="158" t="s">
+        <v>935</v>
+      </c>
+      <c r="I84" s="15" t="s">
+        <v>936</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="K84" s="15" t="s">
+        <v>937</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>938</v>
+      </c>
+      <c r="M84" s="21" t="s">
+        <v>939</v>
+      </c>
+      <c r="N84" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="O84" s="32">
+        <v>36124</v>
+      </c>
+      <c r="P84" s="20" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q84" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="R84" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="S84" s="21">
+        <v>1.614266</v>
+      </c>
+      <c r="T84" s="21">
+        <v>103.612174</v>
+      </c>
+      <c r="U84" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="V84" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W84" s="25" t="s">
+        <v>792</v>
+      </c>
+      <c r="X84" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>84</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" s="11">
+        <v>30000982</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="F85" s="29" t="s">
+        <v>731</v>
+      </c>
+      <c r="G85" s="14">
+        <v>6002325123</v>
+      </c>
+      <c r="H85" s="14" t="s">
+        <v>732</v>
+      </c>
+      <c r="I85" s="15" t="s">
+        <v>733</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="L85" s="143" t="s">
+        <v>735</v>
+      </c>
+      <c r="M85" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="N85" s="18" t="s">
+        <v>737</v>
+      </c>
+      <c r="O85" s="19">
+        <v>80237</v>
+      </c>
+      <c r="P85" s="20" t="s">
+        <v>738</v>
+      </c>
+      <c r="Q85" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="R85" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="S85" s="34">
+        <v>-8.6418359999999996</v>
+      </c>
+      <c r="T85" s="34">
+        <v>115.234284</v>
+      </c>
+      <c r="U85" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="V85" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W85" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X85" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <v>85</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="144">
+        <v>30011151</v>
+      </c>
+      <c r="E86" s="135" t="s">
+        <v>740</v>
+      </c>
+      <c r="F86" s="29" t="s">
+        <v>741</v>
+      </c>
+      <c r="G86" s="14">
+        <v>6020996226</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>742</v>
+      </c>
+      <c r="I86" s="145" t="s">
+        <v>743</v>
+      </c>
+      <c r="J86" s="145" t="s">
+        <v>409</v>
+      </c>
+      <c r="K86" s="145" t="s">
+        <v>744</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>745</v>
+      </c>
+      <c r="M86" s="146" t="s">
+        <v>746</v>
+      </c>
+      <c r="N86" s="147" t="s">
+        <v>747</v>
+      </c>
+      <c r="O86" s="148">
+        <v>84117</v>
+      </c>
+      <c r="P86" s="149" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q86" s="150" t="s">
+        <v>749</v>
+      </c>
+      <c r="R86" s="146" t="s">
+        <v>409</v>
+      </c>
+      <c r="S86" s="151">
+        <v>-8.4565239999999999</v>
+      </c>
+      <c r="T86" s="150">
+        <v>118.73248599999999</v>
+      </c>
+      <c r="U86" s="152" t="s">
+        <v>750</v>
+      </c>
+      <c r="V86" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W86" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X86" s="146" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A87" s="33">
+        <v>86</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" s="153">
+        <v>30076794</v>
+      </c>
+      <c r="E87" s="29" t="s">
+        <v>752</v>
+      </c>
+      <c r="F87" s="101" t="s">
+        <v>752</v>
+      </c>
+      <c r="G87" s="14">
+        <v>6048719838</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>752</v>
+      </c>
+      <c r="I87" s="39" t="s">
+        <v>753</v>
+      </c>
+      <c r="J87" s="39" t="s">
+        <v>501</v>
+      </c>
+      <c r="K87" s="39" t="s">
+        <v>754</v>
+      </c>
+      <c r="L87" s="40" t="s">
+        <v>755</v>
+      </c>
+      <c r="M87" s="22" t="s">
+        <v>756</v>
+      </c>
+      <c r="N87" s="31" t="s">
+        <v>757</v>
+      </c>
+      <c r="O87" s="61">
+        <v>55121</v>
+      </c>
+      <c r="P87" s="154" t="s">
+        <v>758</v>
+      </c>
+      <c r="Q87" s="26" t="s">
+        <v>759</v>
+      </c>
+      <c r="R87" s="26" t="s">
+        <v>760</v>
+      </c>
+      <c r="S87" s="62">
+        <v>-7.8058531410279901</v>
+      </c>
+      <c r="T87" s="62">
+        <v>110.36974667600001</v>
+      </c>
+      <c r="U87" s="121" t="s">
+        <v>38</v>
+      </c>
+      <c r="V87" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W87" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X87" s="22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <v>87</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88" s="153"/>
+      <c r="E88" s="80" t="s">
+        <v>762</v>
+      </c>
+      <c r="F88" s="29" t="s">
+        <v>763</v>
+      </c>
+      <c r="G88" s="14">
+        <v>6032066339</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>764</v>
+      </c>
+      <c r="I88" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="J88" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="K88" s="15" t="s">
+        <v>767</v>
+      </c>
+      <c r="L88" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="M88" s="155" t="s">
+        <v>769</v>
+      </c>
+      <c r="N88" s="31" t="s">
+        <v>770</v>
+      </c>
+      <c r="O88" s="155"/>
+      <c r="P88" s="155"/>
+      <c r="Q88" s="155"/>
+      <c r="R88" s="155"/>
+      <c r="S88" s="155"/>
+      <c r="T88" s="155"/>
+      <c r="U88" s="155"/>
+      <c r="V88" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W88" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X88" s="155"/>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>88</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" s="153"/>
+      <c r="E89" s="80" t="s">
+        <v>772</v>
+      </c>
+      <c r="F89" s="29" t="s">
+        <v>773</v>
+      </c>
+      <c r="G89" s="14">
+        <v>6060304421</v>
+      </c>
+      <c r="H89" s="14" t="s">
+        <v>774</v>
+      </c>
+      <c r="I89" s="52" t="s">
+        <v>775</v>
+      </c>
+      <c r="J89" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="K89" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="L89" s="53" t="s">
+        <v>777</v>
+      </c>
+      <c r="M89" s="155" t="s">
+        <v>778</v>
+      </c>
+      <c r="N89" s="31" t="s">
+        <v>779</v>
+      </c>
+      <c r="O89" s="155"/>
+      <c r="P89" s="155"/>
+      <c r="Q89" s="155"/>
+      <c r="R89" s="155"/>
+      <c r="S89" s="155"/>
+      <c r="T89" s="155"/>
+      <c r="U89" s="155"/>
+      <c r="V89" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W89" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X89" s="155"/>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A90" s="185">
+        <v>89</v>
+      </c>
+      <c r="B90" s="186" t="s">
+        <v>942</v>
+      </c>
+      <c r="C90" s="187" t="s">
+        <v>943</v>
+      </c>
+      <c r="E90" t="s">
+        <v>944</v>
+      </c>
+      <c r="F90" s="188" t="s">
+        <v>944</v>
+      </c>
+      <c r="I90" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation operator="equal" allowBlank="1" sqref="M19:O20" xr:uid="{DBE8A90A-52AC-4260-8683-B85ED3A65351}">
+    <dataValidation operator="equal" allowBlank="1" sqref="M23:O24" xr:uid="{60C2D957-7A9F-4C33-9097-2739EE8BB737}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation operator="equal" allowBlank="1" sqref="M22:N24 O21:O24 Q22:Q24" xr:uid="{0AFD979A-E49A-4141-A551-D701BAF0FC1A}">
+    <dataValidation operator="equal" allowBlank="1" sqref="M26:N28 O25:O28 Q26:Q28" xr:uid="{C88EDD75-2A7B-4480-911A-7DFD62F83F25}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1" xr:uid="{B7F19B4F-27C2-46A4-8AB1-91868E464995}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{B80FE45D-5928-4D60-825F-4310FD526FF3}"/>
-    <hyperlink ref="N4" r:id="rId3" xr:uid="{72DAE2B7-646F-4D35-B922-707AB4406A41}"/>
-    <hyperlink ref="N5" r:id="rId4" xr:uid="{8B8F4E2F-B4BF-4908-9F33-A21DF4999495}"/>
-    <hyperlink ref="N3" r:id="rId5" xr:uid="{58FD6C65-DBB9-42B9-8478-AB3DD256D9C0}"/>
-    <hyperlink ref="N6" r:id="rId6" xr:uid="{8F4FC14D-F84C-43B3-B3C7-D5BCB4FF85C1}"/>
-    <hyperlink ref="N7" r:id="rId7" xr:uid="{9EFACA75-AD3F-4642-8482-0367F51DD578}"/>
-    <hyperlink ref="N8" r:id="rId8" xr:uid="{EF7DC6D1-31A7-4DDF-AEC8-CB9AF0EE52C0}"/>
-    <hyperlink ref="N9" r:id="rId9" xr:uid="{CD31CDFD-50EF-4E75-B6FD-33D15D64A777}"/>
-    <hyperlink ref="N10" r:id="rId10" xr:uid="{5A42D1EC-249D-4D79-8BE1-5BD3AB4F4BB1}"/>
-    <hyperlink ref="C3:C10" r:id="rId11" display="P@ssw0rd" xr:uid="{DAB366A2-C6A4-4F2B-8D3E-E0407176A618}"/>
-    <hyperlink ref="N11" r:id="rId12" xr:uid="{E9BFD1AF-7BD7-4EEA-8540-68961E1FF08B}"/>
-    <hyperlink ref="N12" r:id="rId13" xr:uid="{D5C5A345-515D-4EF1-8A1B-FD3E0232356D}"/>
-    <hyperlink ref="N13" r:id="rId14" xr:uid="{9B10F84B-A800-4EDB-AD49-9B1AAB25636F}"/>
-    <hyperlink ref="N14" r:id="rId15" xr:uid="{A9AD4C5B-CAD1-48C3-A9A6-65ED43ACE901}"/>
-    <hyperlink ref="N15" r:id="rId16" xr:uid="{BBDEEE1C-55F9-4297-88E0-56CA76B26080}"/>
-    <hyperlink ref="N16" r:id="rId17" xr:uid="{C5EF87C1-EA06-4CBB-B762-961142A9D8B0}"/>
-    <hyperlink ref="N17" r:id="rId18" xr:uid="{5612DFDD-E8E5-48C1-9959-AE2594D50F3E}"/>
-    <hyperlink ref="N18" r:id="rId19" xr:uid="{90A3BB1C-8B8E-442E-9CF3-7DF9429010CA}"/>
-    <hyperlink ref="C11:C18" r:id="rId20" display="P@ssw0rd" xr:uid="{939D7807-F508-4785-9CB8-A8B7301BF601}"/>
-    <hyperlink ref="N19" r:id="rId21" xr:uid="{5D3FD158-F93E-44B0-8D11-F0481D1F47E0}"/>
-    <hyperlink ref="N20" r:id="rId22" xr:uid="{B574641F-7F0C-48C4-8858-497E89870AB5}"/>
-    <hyperlink ref="N21" r:id="rId23" xr:uid="{E846E3A3-AD00-4ED5-89DE-DDD38481B71A}"/>
-    <hyperlink ref="N22" r:id="rId24" xr:uid="{600034C5-B884-4480-A0E9-6F77D46610E5}"/>
-    <hyperlink ref="N23" r:id="rId25" xr:uid="{B5F5A3BD-D34F-4A31-9638-040B5B98A5F7}"/>
-    <hyperlink ref="N24" r:id="rId26" xr:uid="{2F352CFC-991D-4A2C-9F2D-8F17A9D81D18}"/>
-    <hyperlink ref="N25" r:id="rId27" xr:uid="{7303657B-C3E9-41CD-ABD1-3025FD385F6C}"/>
-    <hyperlink ref="N26" r:id="rId28" xr:uid="{674EC7E2-4B15-4920-A4FA-BFF98E5397BE}"/>
-    <hyperlink ref="N27" r:id="rId29" xr:uid="{7306F67A-E4B0-40FB-8644-F328A8A619B3}"/>
-    <hyperlink ref="N28" r:id="rId30" xr:uid="{0DD8A9D2-1187-4280-93DD-62C34D046733}"/>
-    <hyperlink ref="N29" r:id="rId31" xr:uid="{2185303A-60B0-4217-9906-E675B271E0FC}"/>
-    <hyperlink ref="C19:C29" r:id="rId32" display="P@ssw0rd" xr:uid="{4C7C6A1B-0F1C-4A80-B5AE-CD0E5DAA4522}"/>
-    <hyperlink ref="N30" r:id="rId33" xr:uid="{612862EE-859D-4FA5-9093-8803706F30AF}"/>
-    <hyperlink ref="C30" r:id="rId34" xr:uid="{669A9B26-EE8C-49B2-9479-EF0166436B4E}"/>
-    <hyperlink ref="N31" r:id="rId35" xr:uid="{F9E64CB5-974D-44C0-9D48-0BE86653E4E5}"/>
-    <hyperlink ref="N32" r:id="rId36" xr:uid="{E11E172B-53F5-43CD-975A-D590AA91AD0A}"/>
-    <hyperlink ref="N34" r:id="rId37" xr:uid="{A6821A06-DBDB-4D95-8A02-87FD66255363}"/>
-    <hyperlink ref="N33" r:id="rId38" xr:uid="{AC2611DD-05C4-40B6-8B05-8B94D350745A}"/>
-    <hyperlink ref="N35" r:id="rId39" xr:uid="{B2298E08-0949-4149-B22D-7166F98EA2A5}"/>
-    <hyperlink ref="N36" r:id="rId40" xr:uid="{A4A214EF-51F8-4C98-B45A-9D573A3AF4BD}"/>
-    <hyperlink ref="N37" r:id="rId41" xr:uid="{82CB1463-D717-4ED0-A152-6ECED7AD13A3}"/>
-    <hyperlink ref="N38" r:id="rId42" xr:uid="{372B920A-945E-47B4-BA66-3009E1571264}"/>
-    <hyperlink ref="N39" r:id="rId43" xr:uid="{57611076-4B42-49F2-8C1E-4600DFADC84D}"/>
-    <hyperlink ref="N40" r:id="rId44" xr:uid="{033C8158-9D9C-430F-AC78-FAE938B467D1}"/>
-    <hyperlink ref="N41" r:id="rId45" xr:uid="{81C8131E-14BF-409C-89D5-A2C337CC5248}"/>
-    <hyperlink ref="N42" r:id="rId46" xr:uid="{96F0C25D-66D2-4AA7-8A18-1F089D5406B1}"/>
-    <hyperlink ref="N43" r:id="rId47" xr:uid="{5419296C-10EE-4E6E-B337-448ED9FEAFF4}"/>
-    <hyperlink ref="C31:C43" r:id="rId48" display="P@ssw0rd" xr:uid="{D31BD56B-F3D2-49CF-BCAB-2C5DE7DE5185}"/>
-    <hyperlink ref="N44" r:id="rId49" xr:uid="{3C4AE44E-7E93-4987-9A5D-517A3FBB55CE}"/>
-    <hyperlink ref="N45" r:id="rId50" xr:uid="{C2FA829B-C7C9-4CE8-8CB1-5C2D80543DFA}"/>
-    <hyperlink ref="N46" r:id="rId51" xr:uid="{DF1DC381-8D64-4747-96A6-7DF7169A17B4}"/>
-    <hyperlink ref="N47" r:id="rId52" xr:uid="{42B78578-7F36-484E-97FB-7FE1B0078045}"/>
-    <hyperlink ref="N48" r:id="rId53" xr:uid="{0EDC2B9F-7248-4C97-AFD4-D994B385C9C7}"/>
-    <hyperlink ref="C44:C48" r:id="rId54" display="P@ssw0rd" xr:uid="{A2DC6E58-4D49-41C5-BE33-0ADA0E2D3433}"/>
-    <hyperlink ref="N49" r:id="rId55" xr:uid="{62132758-B449-4CC1-93E6-1DDC4BF14315}"/>
-    <hyperlink ref="N50" r:id="rId56" xr:uid="{2891B74B-8141-4D3B-991B-09A6367F3A3A}"/>
-    <hyperlink ref="N51" r:id="rId57" xr:uid="{64D95F10-289D-4A05-94E1-F3B285DCE84E}"/>
-    <hyperlink ref="N52" r:id="rId58" xr:uid="{46DF84F3-912F-4A43-9A08-45291DAC2759}"/>
-    <hyperlink ref="N53" r:id="rId59" xr:uid="{09E41371-689F-4E0A-BA76-6BFC5B5C85A9}"/>
-    <hyperlink ref="N54" r:id="rId60" xr:uid="{CE94F203-2DF0-4616-80BF-1CBCF8F2A8AD}"/>
-    <hyperlink ref="C49:C54" r:id="rId61" display="P@ssw0rd" xr:uid="{219F7957-41CB-43AA-B9B4-2BB92C9E110F}"/>
-    <hyperlink ref="N55" r:id="rId62" xr:uid="{98DE0417-F224-43BF-B9E0-9EBA57D27025}"/>
-    <hyperlink ref="N56" r:id="rId63" xr:uid="{45542926-BC3E-4792-B237-4C97B07B6FEB}"/>
-    <hyperlink ref="N57" r:id="rId64" xr:uid="{4FE4E2BF-7549-4FC8-8086-BF4DF9D124D0}"/>
-    <hyperlink ref="N58" r:id="rId65" xr:uid="{F549CD21-2B0F-48D8-ABFE-DC44D8288E0E}"/>
-    <hyperlink ref="N59" r:id="rId66" xr:uid="{EC71CB2B-ECC6-4DA0-A0A0-28E35EBD31E7}"/>
-    <hyperlink ref="C55:C59" r:id="rId67" display="P@ssw0rd" xr:uid="{84810F95-8E76-4C9C-B196-BB069B9EF1DB}"/>
-    <hyperlink ref="N60" r:id="rId68" xr:uid="{2C6E8507-0089-4D4B-A4C9-D4A9C37A6CFC}"/>
-    <hyperlink ref="C60" r:id="rId69" xr:uid="{9A283477-0043-4329-87BD-FB1DE2EF1FE6}"/>
-    <hyperlink ref="N61" r:id="rId70" xr:uid="{CAA7FF67-9E05-4D61-AAAE-D6194CB3C95A}"/>
-    <hyperlink ref="C61" r:id="rId71" xr:uid="{F341833F-E4AC-404A-8AC7-29BDC4027157}"/>
-    <hyperlink ref="N62" r:id="rId72" xr:uid="{6D68A806-164F-4343-8D3A-D0216B43E3DE}"/>
-    <hyperlink ref="N63" r:id="rId73" xr:uid="{7458C434-A716-480B-830E-59263B9B2830}"/>
-    <hyperlink ref="N64" r:id="rId74" xr:uid="{151A620C-3EF6-47BE-B9F1-BB028202877F}"/>
-    <hyperlink ref="N65" r:id="rId75" xr:uid="{C276CE8D-10CB-475C-9409-3E8FEFA60B39}"/>
-    <hyperlink ref="C62:C65" r:id="rId76" display="P@ssw0rd" xr:uid="{9F5946EA-CA10-489C-B000-63F74BFF2F9B}"/>
-    <hyperlink ref="N66" r:id="rId77" xr:uid="{BA9BCA0B-9D7D-40FE-A56B-E1829074D01F}"/>
-    <hyperlink ref="N67" r:id="rId78" xr:uid="{198DDA39-9EA1-44CA-9B42-BD5A5FCB00FF}"/>
-    <hyperlink ref="C66:C67" r:id="rId79" display="P@ssw0rd" xr:uid="{B6F990AC-BA79-4183-BFB4-4FEDFA5C3C50}"/>
-    <hyperlink ref="N68" r:id="rId80" xr:uid="{0BF01F9F-9038-4E73-9F0D-518384908E75}"/>
-    <hyperlink ref="N69" r:id="rId81" xr:uid="{42F450C2-7A8A-4A23-BC45-B9CBB4A0EB62}"/>
-    <hyperlink ref="N70" r:id="rId82" xr:uid="{5E8977A1-150F-4150-8F96-0F9975B34464}"/>
-    <hyperlink ref="N71" r:id="rId83" xr:uid="{FB63338E-1CA4-4B01-B416-F52E744BA733}"/>
-    <hyperlink ref="N72" r:id="rId84" xr:uid="{84CF6559-BBF8-429C-9801-C5DE7CA103CD}"/>
-    <hyperlink ref="C68:C72" r:id="rId85" display="P@ssw0rd" xr:uid="{93235752-BE64-43A7-A226-172FB89DD5BC}"/>
+    <hyperlink ref="N6" r:id="rId1" xr:uid="{EFBA725E-DA51-4811-AE5B-EAAA8A15D5BF}"/>
+    <hyperlink ref="N7" r:id="rId2" xr:uid="{BAAFF5A3-4303-4BF9-B2B1-2C8D3156E1AF}"/>
+    <hyperlink ref="N5" r:id="rId3" xr:uid="{24969A80-A986-4938-B03F-35571F9CD1E4}"/>
+    <hyperlink ref="N4" r:id="rId4" xr:uid="{53C24032-7758-4DB5-9492-A42153E1E163}"/>
+    <hyperlink ref="N3" r:id="rId5" xr:uid="{8ED244FC-1E28-440D-BD13-D59CC81FA441}"/>
+    <hyperlink ref="N8" r:id="rId6" xr:uid="{EF110F3D-66F6-4047-AC93-0D2DFD6F3A1C}"/>
+    <hyperlink ref="N9" r:id="rId7" xr:uid="{F811A3E1-1045-4ACE-9D09-90886F510FA6}"/>
+    <hyperlink ref="N10" r:id="rId8" xr:uid="{E6B0D366-2DC1-4C04-91BF-75D2AC62F4FD}"/>
+    <hyperlink ref="N11" r:id="rId9" xr:uid="{97163FD9-1178-4F13-B271-495FA41A0D01}"/>
+    <hyperlink ref="N12" r:id="rId10" xr:uid="{3B719601-901F-4F8B-B196-624A3AD81526}"/>
+    <hyperlink ref="N13" r:id="rId11" xr:uid="{FA1CE031-3AEA-4BBE-BE5D-7B3233CEECAB}"/>
+    <hyperlink ref="N14" r:id="rId12" xr:uid="{83741760-9300-4381-94E7-B068F199E86E}"/>
+    <hyperlink ref="N15" r:id="rId13" xr:uid="{CA5DC0D1-C359-4AA2-A9F1-279875BC1360}"/>
+    <hyperlink ref="N16" r:id="rId14" xr:uid="{31C15EF4-C4CE-4847-BF76-35595DE34FC8}"/>
+    <hyperlink ref="N17" r:id="rId15" xr:uid="{9C7E6FB9-6BF1-45A3-A8A5-A059ECF08BA4}"/>
+    <hyperlink ref="N18" r:id="rId16" xr:uid="{A55363FC-DE46-4826-9765-B622E9FD7FDF}"/>
+    <hyperlink ref="N19" r:id="rId17" xr:uid="{B819539E-397A-4E6D-8E78-FDE3F83E60F2}"/>
+    <hyperlink ref="N20" r:id="rId18" xr:uid="{F80AB18B-A1D8-4CDD-8B7C-41ADFC4A708B}"/>
+    <hyperlink ref="N21" r:id="rId19" xr:uid="{3A3E36E1-85D8-4E6D-BD77-82C76B33A391}"/>
+    <hyperlink ref="N22" r:id="rId20" xr:uid="{1BC67918-60D9-44DE-9D51-7E4BE373784D}"/>
+    <hyperlink ref="N23" r:id="rId21" xr:uid="{228607BE-6929-459A-B850-F9B6AB8DF6D5}"/>
+    <hyperlink ref="N24" r:id="rId22" xr:uid="{66096E62-8C39-4419-8D55-E49F0542E934}"/>
+    <hyperlink ref="N25" r:id="rId23" xr:uid="{2E190F0C-5D35-46F5-982C-CD567650A4E3}"/>
+    <hyperlink ref="N26" r:id="rId24" xr:uid="{CA457F86-68FB-4FF2-ABC7-B3DDE1B28F23}"/>
+    <hyperlink ref="N27" r:id="rId25" xr:uid="{D9EFDB5D-BB6A-4D22-B762-839E0FAC8A02}"/>
+    <hyperlink ref="N28" r:id="rId26" xr:uid="{DCA85759-2A2F-4630-A597-330FF9B42679}"/>
+    <hyperlink ref="N29" r:id="rId27" xr:uid="{5ADE249C-0567-4DB0-954C-F40FDEDD18E5}"/>
+    <hyperlink ref="N30" r:id="rId28" xr:uid="{02EDE092-C003-42A6-8F2E-99BE0DA396CA}"/>
+    <hyperlink ref="N31" r:id="rId29" xr:uid="{57AC7B2C-5A36-4BB9-A0F2-5B08F3C26D3C}"/>
+    <hyperlink ref="N2" r:id="rId30" xr:uid="{9FBD979E-883B-4729-82DF-68D7CB06A2FE}"/>
+    <hyperlink ref="N32" r:id="rId31" xr:uid="{2CB2FFF4-32F7-4B1E-A45F-764F7C66C197}"/>
+    <hyperlink ref="N33" r:id="rId32" xr:uid="{0E7253C7-0618-42D8-9115-C4036B164F9C}"/>
+    <hyperlink ref="N34" r:id="rId33" xr:uid="{B5F4B497-B71D-460D-B6B4-B70A76BB19E6}"/>
+    <hyperlink ref="N35" r:id="rId34" xr:uid="{3A0B96E8-6E98-42D0-9EE3-19983030BAE9}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{7658DA49-B275-477D-9D75-500315010EE9}"/>
+    <hyperlink ref="N37" r:id="rId36" xr:uid="{9D53FD6C-324F-407A-8E18-CC23FE27CB05}"/>
+    <hyperlink ref="N38" r:id="rId37" xr:uid="{470609E0-6FA3-4233-8E6D-FD922A3982FC}"/>
+    <hyperlink ref="N40" r:id="rId38" xr:uid="{4E516F1C-0023-48C8-87A0-B97E6644C5A7}"/>
+    <hyperlink ref="N39" r:id="rId39" xr:uid="{5420C232-AE9F-4C7D-8F79-A1AE719DDF59}"/>
+    <hyperlink ref="N41" r:id="rId40" xr:uid="{B061D4AB-0213-4D14-943E-075E8AFE17F9}"/>
+    <hyperlink ref="N42" r:id="rId41" xr:uid="{A36E9926-7267-441E-92A6-B2FE7F70B569}"/>
+    <hyperlink ref="N43" r:id="rId42" xr:uid="{357F4765-9D94-4548-94CC-12F9B8E90A96}"/>
+    <hyperlink ref="N44" r:id="rId43" xr:uid="{B8310E75-5405-4083-A0CD-84D608091415}"/>
+    <hyperlink ref="N45" r:id="rId44" xr:uid="{F7DB1F30-3D04-4396-8AD4-0FE6D08ABE27}"/>
+    <hyperlink ref="N46" r:id="rId45" xr:uid="{8F762870-3956-4FB0-8A1B-DFA0F68D2AB5}"/>
+    <hyperlink ref="N47" r:id="rId46" xr:uid="{4090DC1E-C99B-44A4-BC22-3CD4ABD08C10}"/>
+    <hyperlink ref="N48" r:id="rId47" xr:uid="{8FA64235-9B1D-47AC-BD6F-3589399ACEF5}"/>
+    <hyperlink ref="N49" r:id="rId48" xr:uid="{7D1A835C-3A69-4596-98BB-0C5B023DF949}"/>
+    <hyperlink ref="N50" r:id="rId49" xr:uid="{54D67FD6-7E02-4858-B111-D16D49523404}"/>
+    <hyperlink ref="N51" r:id="rId50" xr:uid="{9AC82D1B-BCE9-4A75-B96C-979B364F7D81}"/>
+    <hyperlink ref="N52" r:id="rId51" xr:uid="{6402D651-FCBA-4507-A1FE-4E3574B2404A}"/>
+    <hyperlink ref="N53" r:id="rId52" xr:uid="{C7CD3C7C-40BA-4F96-B5E4-7212D7FDEDD5}"/>
+    <hyperlink ref="N54" r:id="rId53" xr:uid="{817DC17F-F37E-40E8-8A67-0F874C44C802}"/>
+    <hyperlink ref="N55" r:id="rId54" xr:uid="{66FB437E-D6A3-4F62-9F5B-8DC0611F33C5}"/>
+    <hyperlink ref="N56" r:id="rId55" xr:uid="{E99D733A-DF22-47EF-8575-08F664E5D82E}"/>
+    <hyperlink ref="N57" r:id="rId56" xr:uid="{23C8324B-3105-47B2-923E-5BAF7F25D749}"/>
+    <hyperlink ref="N58" r:id="rId57" xr:uid="{CDBDCE43-3C94-40EE-8D66-11337BC17ACD}"/>
+    <hyperlink ref="N59" r:id="rId58" xr:uid="{A244C4CC-D653-4BD5-BAD5-D1D08907E5F3}"/>
+    <hyperlink ref="N60" r:id="rId59" xr:uid="{F8B501DE-278F-4E51-9B62-5FA169B3EACA}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{8B6A06CC-7F4E-4442-8C99-87C32920DCDC}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{A3BE2D01-6A5A-4F2A-B895-75DA1EEA6903}"/>
+    <hyperlink ref="N63" r:id="rId62" xr:uid="{83964CE7-264E-4AEA-A38A-52D4E331DEBF}"/>
+    <hyperlink ref="N64" r:id="rId63" xr:uid="{A0A48AD5-0935-48A0-840A-9298E5347E80}"/>
+    <hyperlink ref="N65" r:id="rId64" xr:uid="{54435A90-641A-48F1-A10F-FF36C8BB8FC7}"/>
+    <hyperlink ref="N66" r:id="rId65" xr:uid="{E60CF90A-7ABA-465A-B458-F63FD0E02307}"/>
+    <hyperlink ref="N67" r:id="rId66" xr:uid="{50616B53-F10C-4D68-9FDD-CC4DF5FFCFF7}"/>
+    <hyperlink ref="N68" r:id="rId67" xr:uid="{AAFE6E5C-1DFB-4A41-9BF6-ED9006DECA95}"/>
+    <hyperlink ref="N69" r:id="rId68" xr:uid="{D1717AEE-A0DD-4140-8090-DD44B380F827}"/>
+    <hyperlink ref="N70" r:id="rId69" xr:uid="{E6202F4B-7B19-4A7B-9EDD-11AE4AC570EE}"/>
+    <hyperlink ref="N71" r:id="rId70" xr:uid="{66848B45-CE0C-4553-818A-D8AEBEBC350F}"/>
+    <hyperlink ref="N72" r:id="rId71" xr:uid="{F949D1B9-814F-41D1-8B15-1FBB69DF21F7}"/>
+    <hyperlink ref="N73" r:id="rId72" xr:uid="{33EBB15C-B95B-4B9F-99FE-6AAEB375C50B}"/>
+    <hyperlink ref="N74" r:id="rId73" xr:uid="{26F89070-F71D-4C77-8C7B-A968407850C6}"/>
+    <hyperlink ref="N75" r:id="rId74" xr:uid="{6A57C089-8933-47E4-8532-BBF8F20178A7}"/>
+    <hyperlink ref="N76" r:id="rId75" xr:uid="{8A6E52F4-0910-48FE-A5B9-86C709F3AA40}"/>
+    <hyperlink ref="N77" r:id="rId76" xr:uid="{29726FA0-DB0E-4532-8A65-53EB6C963A9F}"/>
+    <hyperlink ref="N78" r:id="rId77" xr:uid="{980ABB41-D92A-46F2-BD9C-9FC3E23339EF}"/>
+    <hyperlink ref="N79" r:id="rId78" xr:uid="{8734793D-1A85-4B3D-BF31-A77588FBBD77}"/>
+    <hyperlink ref="N80" r:id="rId79" xr:uid="{CA897975-D812-47C6-941B-54D63458DB52}"/>
+    <hyperlink ref="N81" r:id="rId80" xr:uid="{ECB147EB-95F1-4AE2-A04E-ABE90EA07763}"/>
+    <hyperlink ref="N82" r:id="rId81" xr:uid="{31FB1699-19FC-42C5-815F-CED64EADEE9B}"/>
+    <hyperlink ref="N83" r:id="rId82" xr:uid="{839FC9F5-A5C1-42F5-B54C-0B2972790E8A}"/>
+    <hyperlink ref="N84" r:id="rId83" xr:uid="{5E95373C-5BB8-4289-AE2F-FB759873C5F7}"/>
+    <hyperlink ref="N85" r:id="rId84" xr:uid="{793A8DF9-23FD-4B15-8E90-C63D25856D50}"/>
+    <hyperlink ref="N86" r:id="rId85" xr:uid="{51362116-859F-4170-9377-8A64631A9C02}"/>
+    <hyperlink ref="N87" r:id="rId86" xr:uid="{8C64DA85-71CC-485A-B43B-4B634C085A6A}"/>
+    <hyperlink ref="N88" r:id="rId87" xr:uid="{764E1EAB-8D69-45B2-A105-6E6048F86697}"/>
+    <hyperlink ref="N89" r:id="rId88" xr:uid="{25C9918E-1D19-41D7-BEE9-C8E05FE16BED}"/>
+    <hyperlink ref="C2" r:id="rId89" xr:uid="{8CC8DA8D-7EF6-4F9A-9BF6-73DD0EDEBB0D}"/>
+    <hyperlink ref="C3:C89" r:id="rId90" display="P@ssw0rd" xr:uid="{A6CEE2D1-A918-488C-BD42-4035BE55B9A9}"/>
+    <hyperlink ref="C90" r:id="rId91" display="P@ssw0rd" xr:uid="{8D95530F-BF60-4708-8A13-91E275C2EDF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
